--- a/research/traditional_assets/database/data/nigeria/nigeria_trucking.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_trucking.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.164525450597881</v>
+        <v>0.1640633742460873</v>
       </c>
       <c r="C2">
-        <v>3.052988084438175</v>
+        <v>3.034777469090573</v>
       </c>
       <c r="D2">
-        <v>2.914988084438175</v>
+        <v>2.926377469090573</v>
       </c>
       <c r="E2">
-        <v>-1.05</v>
+        <v>-1.0204</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0296</v>
       </c>
       <c r="G2">
         <v>0.138</v>
@@ -1445,28 +1445,28 @@
         <v>1.168</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00148888</v>
       </c>
       <c r="N2">
-        <v>1.168</v>
+        <v>1.16651112</v>
       </c>
       <c r="O2">
-        <v>0.3504</v>
+        <v>0.349953336</v>
       </c>
       <c r="P2">
-        <v>0.8175999999999999</v>
+        <v>0.816557784</v>
       </c>
       <c r="Q2">
-        <v>0.8095999999999999</v>
+        <v>0.808557784</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.164525450597881</v>
+        <v>0.1653649234808963</v>
       </c>
       <c r="T2">
-        <v>0.8278063840919477</v>
+        <v>0.833659560545123</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>784.4822954166891</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1640633742460873</v>
+        <v>0.1636012978942936</v>
       </c>
       <c r="C3">
-        <v>3.034777469090573</v>
+        <v>3.016656203612682</v>
       </c>
       <c r="D3">
-        <v>2.926377469090573</v>
+        <v>2.937856203612683</v>
       </c>
       <c r="E3">
-        <v>-1.0204</v>
+        <v>-0.9908</v>
       </c>
       <c r="F3">
-        <v>0.0296</v>
+        <v>0.0592</v>
       </c>
       <c r="G3">
         <v>0.138</v>
@@ -1527,28 +1527,28 @@
         <v>1.168</v>
       </c>
       <c r="M3">
-        <v>0.00148888</v>
+        <v>0.00297776</v>
       </c>
       <c r="N3">
-        <v>1.16651112</v>
+        <v>1.16502224</v>
       </c>
       <c r="O3">
-        <v>0.349953336</v>
+        <v>0.349506672</v>
       </c>
       <c r="P3">
-        <v>0.816557784</v>
+        <v>0.8155155679999999</v>
       </c>
       <c r="Q3">
-        <v>0.808557784</v>
+        <v>0.8075155679999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1653649234808963</v>
+        <v>0.166221528463565</v>
       </c>
       <c r="T3">
-        <v>0.833659560545123</v>
+        <v>0.8396321895789756</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>784.4822954166891</v>
+        <v>392.2411477083445</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1636012978942936</v>
+        <v>0.1631392215425</v>
       </c>
       <c r="C4">
-        <v>3.016656203612682</v>
+        <v>2.998625343571293</v>
       </c>
       <c r="D4">
-        <v>2.937856203612683</v>
+        <v>2.949425343571293</v>
       </c>
       <c r="E4">
-        <v>-0.9908</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="F4">
-        <v>0.0592</v>
+        <v>0.08879999999999999</v>
       </c>
       <c r="G4">
         <v>0.138</v>
@@ -1609,28 +1609,28 @@
         <v>1.168</v>
       </c>
       <c r="M4">
-        <v>0.00297776</v>
+        <v>0.004466639999999999</v>
       </c>
       <c r="N4">
-        <v>1.16502224</v>
+        <v>1.16353336</v>
       </c>
       <c r="O4">
-        <v>0.349506672</v>
+        <v>0.349060008</v>
       </c>
       <c r="P4">
-        <v>0.8155155679999999</v>
+        <v>0.814473352</v>
       </c>
       <c r="Q4">
-        <v>0.8075155679999999</v>
+        <v>0.806473352</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.166221528463565</v>
+        <v>0.1670957954046392</v>
       </c>
       <c r="T4">
-        <v>0.8396321895789756</v>
+        <v>0.8457279656032166</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>392.2411477083445</v>
+        <v>261.4940984722297</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1631392215425</v>
+        <v>0.1626771451907064</v>
       </c>
       <c r="C5">
-        <v>2.998625343571293</v>
+        <v>2.980685961226023</v>
       </c>
       <c r="D5">
-        <v>2.949425343571293</v>
+        <v>2.961085961226023</v>
       </c>
       <c r="E5">
-        <v>-0.9612000000000001</v>
+        <v>-0.9316</v>
       </c>
       <c r="F5">
-        <v>0.08879999999999999</v>
+        <v>0.1184</v>
       </c>
       <c r="G5">
         <v>0.138</v>
@@ -1691,28 +1691,28 @@
         <v>1.168</v>
       </c>
       <c r="M5">
-        <v>0.004466639999999999</v>
+        <v>0.00595552</v>
       </c>
       <c r="N5">
-        <v>1.16353336</v>
+        <v>1.16204448</v>
       </c>
       <c r="O5">
-        <v>0.349060008</v>
+        <v>0.3486133439999999</v>
       </c>
       <c r="P5">
-        <v>0.814473352</v>
+        <v>0.8134311359999999</v>
       </c>
       <c r="Q5">
-        <v>0.806473352</v>
+        <v>0.8054311359999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1670957954046392</v>
+        <v>0.1679882762403191</v>
       </c>
       <c r="T5">
-        <v>0.8457279656032166</v>
+        <v>0.8519507369612961</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>261.4940984722297</v>
+        <v>196.1205738541722</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1626771451907064</v>
+        <v>0.1622150688389127</v>
       </c>
       <c r="C6">
-        <v>2.980685961226023</v>
+        <v>2.962839145860599</v>
       </c>
       <c r="D6">
-        <v>2.961085961226023</v>
+        <v>2.9728391458606</v>
       </c>
       <c r="E6">
-        <v>-0.9316</v>
+        <v>-0.902</v>
       </c>
       <c r="F6">
-        <v>0.1184</v>
+        <v>0.148</v>
       </c>
       <c r="G6">
         <v>0.138</v>
@@ -1773,28 +1773,28 @@
         <v>1.168</v>
       </c>
       <c r="M6">
-        <v>0.00595552</v>
+        <v>0.007444399999999999</v>
       </c>
       <c r="N6">
-        <v>1.16204448</v>
+        <v>1.1605556</v>
       </c>
       <c r="O6">
-        <v>0.3486133439999999</v>
+        <v>0.34816668</v>
       </c>
       <c r="P6">
-        <v>0.8134311359999999</v>
+        <v>0.81238892</v>
       </c>
       <c r="Q6">
-        <v>0.8054311359999999</v>
+        <v>0.80438892</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1679882762403191</v>
+        <v>0.1688995461462239</v>
       </c>
       <c r="T6">
-        <v>0.8519507369612961</v>
+        <v>0.8583045140321773</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>196.1205738541722</v>
+        <v>156.8964590833378</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1622150688389127</v>
+        <v>0.1617529924871191</v>
       </c>
       <c r="C7">
-        <v>2.962839145860599</v>
+        <v>2.945086004122073</v>
       </c>
       <c r="D7">
-        <v>2.9728391458606</v>
+        <v>2.984686004122073</v>
       </c>
       <c r="E7">
-        <v>-0.902</v>
+        <v>-0.8724000000000001</v>
       </c>
       <c r="F7">
-        <v>0.148</v>
+        <v>0.1776</v>
       </c>
       <c r="G7">
         <v>0.138</v>
@@ -1855,28 +1855,28 @@
         <v>1.168</v>
       </c>
       <c r="M7">
-        <v>0.007444399999999999</v>
+        <v>0.00893328</v>
       </c>
       <c r="N7">
-        <v>1.1605556</v>
+        <v>1.15906672</v>
       </c>
       <c r="O7">
-        <v>0.34816668</v>
+        <v>0.347720016</v>
       </c>
       <c r="P7">
-        <v>0.81238892</v>
+        <v>0.811346704</v>
       </c>
       <c r="Q7">
-        <v>0.80438892</v>
+        <v>0.803346704</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1688995461462239</v>
+        <v>0.1698302047735309</v>
       </c>
       <c r="T7">
-        <v>0.8583045140321773</v>
+        <v>0.8647934778492474</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>156.8964590833378</v>
+        <v>130.7470492361148</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1617529924871191</v>
+        <v>0.1612909161353255</v>
       </c>
       <c r="C8">
-        <v>2.945086004122073</v>
+        <v>2.927427660368165</v>
       </c>
       <c r="D8">
-        <v>2.984686004122073</v>
+        <v>2.996627660368165</v>
       </c>
       <c r="E8">
-        <v>-0.8724000000000001</v>
+        <v>-0.8428000000000001</v>
       </c>
       <c r="F8">
-        <v>0.1776</v>
+        <v>0.2072</v>
       </c>
       <c r="G8">
         <v>0.138</v>
@@ -1937,28 +1937,28 @@
         <v>1.168</v>
       </c>
       <c r="M8">
-        <v>0.008933279999999998</v>
+        <v>0.01042216</v>
       </c>
       <c r="N8">
-        <v>1.15906672</v>
+        <v>1.15757784</v>
       </c>
       <c r="O8">
-        <v>0.347720016</v>
+        <v>0.3472733519999999</v>
       </c>
       <c r="P8">
-        <v>0.811346704</v>
+        <v>0.8103044879999999</v>
       </c>
       <c r="Q8">
-        <v>0.803346704</v>
+        <v>0.8023044879999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1698302047735309</v>
+        <v>0.1707808775648661</v>
       </c>
       <c r="T8">
-        <v>0.8647934778492474</v>
+        <v>0.8714219892752869</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>130.7470492361149</v>
+        <v>112.0688993452413</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1612909161353254</v>
+        <v>0.1608288397835319</v>
       </c>
       <c r="C9">
-        <v>2.927427660368166</v>
+        <v>2.90986525702299</v>
       </c>
       <c r="D9">
-        <v>2.996627660368166</v>
+        <v>3.008665257022991</v>
       </c>
       <c r="E9">
-        <v>-0.8428</v>
+        <v>-0.8132</v>
       </c>
       <c r="F9">
-        <v>0.2072</v>
+        <v>0.2368</v>
       </c>
       <c r="G9">
         <v>0.138</v>
@@ -2019,28 +2019,28 @@
         <v>1.168</v>
       </c>
       <c r="M9">
-        <v>0.01042216</v>
+        <v>0.01191104</v>
       </c>
       <c r="N9">
-        <v>1.15757784</v>
+        <v>1.15608896</v>
       </c>
       <c r="O9">
-        <v>0.3472733519999999</v>
+        <v>0.346826688</v>
       </c>
       <c r="P9">
-        <v>0.8103044879999999</v>
+        <v>0.809262272</v>
       </c>
       <c r="Q9">
-        <v>0.8023044879999999</v>
+        <v>0.801262272</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1707808775648661</v>
+        <v>0.1717522171560129</v>
       </c>
       <c r="T9">
-        <v>0.8714219892752869</v>
+        <v>0.8781945987758055</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>112.0688993452413</v>
+        <v>98.06028692708612</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1608288397835319</v>
+        <v>0.1603667634317382</v>
       </c>
       <c r="C10">
-        <v>2.90986525702299</v>
+        <v>2.892399954941396</v>
       </c>
       <c r="D10">
-        <v>3.008665257022991</v>
+        <v>3.020799954941396</v>
       </c>
       <c r="E10">
-        <v>-0.8132</v>
+        <v>-0.7836000000000001</v>
       </c>
       <c r="F10">
-        <v>0.2368</v>
+        <v>0.2664</v>
       </c>
       <c r="G10">
         <v>0.138</v>
@@ -2101,28 +2101,28 @@
         <v>1.168</v>
       </c>
       <c r="M10">
-        <v>0.01191104</v>
+        <v>0.01339992</v>
       </c>
       <c r="N10">
-        <v>1.15608896</v>
+        <v>1.15460008</v>
       </c>
       <c r="O10">
-        <v>0.346826688</v>
+        <v>0.346380024</v>
       </c>
       <c r="P10">
-        <v>0.809262272</v>
+        <v>0.808220056</v>
       </c>
       <c r="Q10">
-        <v>0.801262272</v>
+        <v>0.800220056</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1717522171560129</v>
+        <v>0.1727449048700419</v>
       </c>
       <c r="T10">
-        <v>0.8781945987758055</v>
+        <v>0.8851160568367749</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>98.06028692708612</v>
+        <v>87.16469949074325</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1603667634317382</v>
+        <v>0.1599046870799445</v>
       </c>
       <c r="C11">
-        <v>2.892399954941396</v>
+        <v>2.875032933782132</v>
       </c>
       <c r="D11">
-        <v>3.020799954941396</v>
+        <v>3.033032933782132</v>
       </c>
       <c r="E11">
-        <v>-0.7836000000000001</v>
+        <v>-0.754</v>
       </c>
       <c r="F11">
-        <v>0.2664</v>
+        <v>0.296</v>
       </c>
       <c r="G11">
         <v>0.138</v>
@@ -2183,28 +2183,28 @@
         <v>1.168</v>
       </c>
       <c r="M11">
-        <v>0.01339992</v>
+        <v>0.0148888</v>
       </c>
       <c r="N11">
-        <v>1.15460008</v>
+        <v>1.1531112</v>
       </c>
       <c r="O11">
-        <v>0.346380024</v>
+        <v>0.34593336</v>
       </c>
       <c r="P11">
-        <v>0.808220056</v>
+        <v>0.8071778399999999</v>
       </c>
       <c r="Q11">
-        <v>0.800220056</v>
+        <v>0.7991778399999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1727449048700419</v>
+        <v>0.1737596523110495</v>
       </c>
       <c r="T11">
-        <v>0.8851160568367749</v>
+        <v>0.8921913250768769</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>87.16469949074325</v>
+        <v>78.44822954166891</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1599046870799445</v>
+        <v>0.1594426107281509</v>
       </c>
       <c r="C12">
-        <v>2.875032933782132</v>
+        <v>2.857765392390149</v>
       </c>
       <c r="D12">
-        <v>3.033032933782132</v>
+        <v>3.04536539239015</v>
       </c>
       <c r="E12">
-        <v>-0.754</v>
+        <v>-0.7244</v>
       </c>
       <c r="F12">
-        <v>0.296</v>
+        <v>0.3256</v>
       </c>
       <c r="G12">
         <v>0.138</v>
@@ -2265,28 +2265,28 @@
         <v>1.168</v>
       </c>
       <c r="M12">
-        <v>0.0148888</v>
+        <v>0.01637768</v>
       </c>
       <c r="N12">
-        <v>1.1531112</v>
+        <v>1.15162232</v>
       </c>
       <c r="O12">
-        <v>0.34593336</v>
+        <v>0.345486696</v>
       </c>
       <c r="P12">
-        <v>0.8071778399999999</v>
+        <v>0.8061356239999999</v>
       </c>
       <c r="Q12">
-        <v>0.7991778399999999</v>
+        <v>0.7981356239999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1737596523110495</v>
+        <v>0.1747972030653381</v>
       </c>
       <c r="T12">
-        <v>0.8921913250768769</v>
+        <v>0.8994255881088915</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>78.44822954166891</v>
+        <v>71.31657231060809</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1594426107281509</v>
+        <v>0.1589805343763573</v>
       </c>
       <c r="C13">
-        <v>2.857765392390149</v>
+        <v>2.840598549188251</v>
       </c>
       <c r="D13">
-        <v>3.04536539239015</v>
+        <v>3.057798549188251</v>
       </c>
       <c r="E13">
-        <v>-0.7244</v>
+        <v>-0.6948000000000001</v>
       </c>
       <c r="F13">
-        <v>0.3256</v>
+        <v>0.3552</v>
       </c>
       <c r="G13">
         <v>0.138</v>
@@ -2347,28 +2347,28 @@
         <v>1.168</v>
       </c>
       <c r="M13">
-        <v>0.01637768</v>
+        <v>0.01786656</v>
       </c>
       <c r="N13">
-        <v>1.15162232</v>
+        <v>1.15013344</v>
       </c>
       <c r="O13">
-        <v>0.345486696</v>
+        <v>0.3450400319999999</v>
       </c>
       <c r="P13">
-        <v>0.8061356239999999</v>
+        <v>0.8050934079999998</v>
       </c>
       <c r="Q13">
-        <v>0.7981356239999999</v>
+        <v>0.7970934079999998</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1747972030653381</v>
+        <v>0.1758583345185878</v>
       </c>
       <c r="T13">
-        <v>0.8994255881088915</v>
+        <v>0.9068242662098155</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>71.31657231060809</v>
+        <v>65.37352461805743</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1589805343763573</v>
+        <v>0.1585184580245636</v>
       </c>
       <c r="C14">
-        <v>2.840598549188251</v>
+        <v>2.823533642578377</v>
       </c>
       <c r="D14">
-        <v>3.057798549188251</v>
+        <v>3.070333642578377</v>
       </c>
       <c r="E14">
-        <v>-0.6948000000000001</v>
+        <v>-0.6652</v>
       </c>
       <c r="F14">
-        <v>0.3552</v>
+        <v>0.3848</v>
       </c>
       <c r="G14">
         <v>0.138</v>
@@ -2429,28 +2429,28 @@
         <v>1.168</v>
       </c>
       <c r="M14">
-        <v>0.01786656</v>
+        <v>0.01935544</v>
       </c>
       <c r="N14">
-        <v>1.15013344</v>
+        <v>1.14864456</v>
       </c>
       <c r="O14">
-        <v>0.3450400319999999</v>
+        <v>0.344593368</v>
       </c>
       <c r="P14">
-        <v>0.8050934079999998</v>
+        <v>0.804051192</v>
       </c>
       <c r="Q14">
-        <v>0.7970934079999998</v>
+        <v>0.796051192</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1758583345185878</v>
+        <v>0.176943859798349</v>
       </c>
       <c r="T14">
-        <v>0.9068242662098155</v>
+        <v>0.9143930288647836</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>65.37352461805743</v>
+        <v>60.34479195512992</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1585184580245636</v>
+        <v>0.1580563816727699</v>
       </c>
       <c r="C15">
-        <v>2.823533642578377</v>
+        <v>2.806571931352797</v>
       </c>
       <c r="D15">
-        <v>3.070333642578377</v>
+        <v>3.082971931352797</v>
       </c>
       <c r="E15">
-        <v>-0.6652</v>
+        <v>-0.6355999999999999</v>
       </c>
       <c r="F15">
-        <v>0.3848</v>
+        <v>0.4144</v>
       </c>
       <c r="G15">
         <v>0.138</v>
@@ -2511,28 +2511,28 @@
         <v>1.168</v>
       </c>
       <c r="M15">
-        <v>0.01935544</v>
+        <v>0.02084432</v>
       </c>
       <c r="N15">
-        <v>1.14864456</v>
+        <v>1.14715568</v>
       </c>
       <c r="O15">
-        <v>0.344593368</v>
+        <v>0.344146704</v>
       </c>
       <c r="P15">
-        <v>0.804051192</v>
+        <v>0.8030089760000001</v>
       </c>
       <c r="Q15">
-        <v>0.796051192</v>
+        <v>0.7950089760000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.176943859798349</v>
+        <v>0.1780546298520581</v>
       </c>
       <c r="T15">
-        <v>0.9143930288647836</v>
+        <v>0.9221378092559138</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>60.34479195512992</v>
+        <v>56.03444967262064</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1580563816727699</v>
+        <v>0.1575943053209763</v>
       </c>
       <c r="C16">
-        <v>2.806571931352797</v>
+        <v>2.789714695115508</v>
       </c>
       <c r="D16">
-        <v>3.082971931352797</v>
+        <v>3.095714695115508</v>
       </c>
       <c r="E16">
-        <v>-0.6355999999999999</v>
+        <v>-0.606</v>
       </c>
       <c r="F16">
-        <v>0.4144</v>
+        <v>0.4440000000000001</v>
       </c>
       <c r="G16">
         <v>0.138</v>
@@ -2593,28 +2593,28 @@
         <v>1.168</v>
       </c>
       <c r="M16">
-        <v>0.02084432</v>
+        <v>0.0223332</v>
       </c>
       <c r="N16">
-        <v>1.14715568</v>
+        <v>1.1456668</v>
       </c>
       <c r="O16">
-        <v>0.344146704</v>
+        <v>0.3437000399999999</v>
       </c>
       <c r="P16">
-        <v>0.8030089760000001</v>
+        <v>0.80196676</v>
       </c>
       <c r="Q16">
-        <v>0.7950089760000001</v>
+        <v>0.79396676</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1780546298520581</v>
+        <v>0.1791915356717368</v>
       </c>
       <c r="T16">
-        <v>0.9221378092559138</v>
+        <v>0.9300648197738942</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>56.03444967262064</v>
+        <v>52.29881969444593</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1575943053209763</v>
+        <v>0.1571322289691827</v>
       </c>
       <c r="C17">
-        <v>2.789714695115508</v>
+        <v>2.772963234714126</v>
       </c>
       <c r="D17">
-        <v>3.095714695115508</v>
+        <v>3.108563234714127</v>
       </c>
       <c r="E17">
-        <v>-0.6060000000000001</v>
+        <v>-0.5764</v>
       </c>
       <c r="F17">
-        <v>0.444</v>
+        <v>0.4736</v>
       </c>
       <c r="G17">
         <v>0.138</v>
@@ -2675,28 +2675,28 @@
         <v>1.168</v>
       </c>
       <c r="M17">
-        <v>0.0223332</v>
+        <v>0.02382208</v>
       </c>
       <c r="N17">
-        <v>1.1456668</v>
+        <v>1.14417792</v>
       </c>
       <c r="O17">
-        <v>0.3437000399999999</v>
+        <v>0.343253376</v>
       </c>
       <c r="P17">
-        <v>0.80196676</v>
+        <v>0.8009245439999999</v>
       </c>
       <c r="Q17">
-        <v>0.79396676</v>
+        <v>0.7929245439999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1791915356717368</v>
+        <v>0.1803555106775984</v>
       </c>
       <c r="T17">
-        <v>0.9300648197738942</v>
+        <v>0.9381805686375407</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>52.29881969444594</v>
+        <v>49.03014346354307</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1571322289691827</v>
+        <v>0.156670152617389</v>
       </c>
       <c r="C18">
-        <v>2.772963234714126</v>
+        <v>2.756318872682566</v>
       </c>
       <c r="D18">
-        <v>3.108563234714127</v>
+        <v>3.121518872682566</v>
       </c>
       <c r="E18">
-        <v>-0.5764</v>
+        <v>-0.5468000000000001</v>
       </c>
       <c r="F18">
-        <v>0.4736</v>
+        <v>0.5032</v>
       </c>
       <c r="G18">
         <v>0.138</v>
@@ -2757,28 +2757,28 @@
         <v>1.168</v>
       </c>
       <c r="M18">
-        <v>0.02382208</v>
+        <v>0.02531096</v>
       </c>
       <c r="N18">
-        <v>1.14417792</v>
+        <v>1.14268904</v>
       </c>
       <c r="O18">
-        <v>0.343253376</v>
+        <v>0.342806712</v>
       </c>
       <c r="P18">
-        <v>0.8009245439999999</v>
+        <v>0.7998823279999998</v>
       </c>
       <c r="Q18">
-        <v>0.7929245439999999</v>
+        <v>0.7918823279999998</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1803555106775984</v>
+        <v>0.1815475332739627</v>
       </c>
       <c r="T18">
-        <v>0.9381805686375407</v>
+        <v>0.9464918777147693</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>49.03014346354307</v>
+        <v>46.1460173774523</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.156670152617389</v>
+        <v>0.1562080762655954</v>
       </c>
       <c r="C19">
-        <v>2.756318872682566</v>
+        <v>2.73978295369485</v>
       </c>
       <c r="D19">
-        <v>3.121518872682566</v>
+        <v>3.13458295369485</v>
       </c>
       <c r="E19">
-        <v>-0.5468000000000001</v>
+        <v>-0.5172</v>
       </c>
       <c r="F19">
-        <v>0.5032</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="G19">
         <v>0.138</v>
@@ -2839,28 +2839,28 @@
         <v>1.168</v>
       </c>
       <c r="M19">
-        <v>0.02531096</v>
+        <v>0.02679984</v>
       </c>
       <c r="N19">
-        <v>1.14268904</v>
+        <v>1.14120016</v>
       </c>
       <c r="O19">
-        <v>0.342806712</v>
+        <v>0.342360048</v>
       </c>
       <c r="P19">
-        <v>0.7998823279999998</v>
+        <v>0.7988401119999999</v>
       </c>
       <c r="Q19">
-        <v>0.7918823279999998</v>
+        <v>0.7908401119999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1815475332739627</v>
+        <v>0.1827686295921895</v>
       </c>
       <c r="T19">
-        <v>0.9464918777147693</v>
+        <v>0.9550059016475396</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>46.1460173774523</v>
+        <v>43.58234974537161</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1562080762655954</v>
+        <v>0.1557459999138018</v>
       </c>
       <c r="C20">
-        <v>2.73978295369485</v>
+        <v>2.723356845030354</v>
       </c>
       <c r="D20">
-        <v>3.13458295369485</v>
+        <v>3.147756845030354</v>
       </c>
       <c r="E20">
-        <v>-0.5172000000000001</v>
+        <v>-0.4876</v>
       </c>
       <c r="F20">
-        <v>0.5327999999999999</v>
+        <v>0.5624</v>
       </c>
       <c r="G20">
         <v>0.138</v>
@@ -2921,28 +2921,28 @@
         <v>1.168</v>
       </c>
       <c r="M20">
-        <v>0.02679983999999999</v>
+        <v>0.02828872</v>
       </c>
       <c r="N20">
-        <v>1.14120016</v>
+        <v>1.13971128</v>
       </c>
       <c r="O20">
-        <v>0.342360048</v>
+        <v>0.341913384</v>
       </c>
       <c r="P20">
-        <v>0.7988401119999999</v>
+        <v>0.7977978960000001</v>
       </c>
       <c r="Q20">
-        <v>0.7908401119999999</v>
+        <v>0.7897978960000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1827686295921895</v>
+        <v>0.1840198764367923</v>
       </c>
       <c r="T20">
-        <v>0.9550059016475396</v>
+        <v>0.9637301483934649</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>43.58234974537162</v>
+        <v>41.28854186403627</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1557459999138018</v>
+        <v>0.1552839235620081</v>
       </c>
       <c r="C21">
-        <v>2.723356845030354</v>
+        <v>2.70704193705084</v>
       </c>
       <c r="D21">
-        <v>3.147756845030354</v>
+        <v>3.16104193705084</v>
       </c>
       <c r="E21">
-        <v>-0.4876</v>
+        <v>-0.4580000000000001</v>
       </c>
       <c r="F21">
-        <v>0.5624</v>
+        <v>0.592</v>
       </c>
       <c r="G21">
         <v>0.138</v>
@@ -3003,28 +3003,28 @@
         <v>1.168</v>
       </c>
       <c r="M21">
-        <v>0.02828872</v>
+        <v>0.0297776</v>
       </c>
       <c r="N21">
-        <v>1.13971128</v>
+        <v>1.1382224</v>
       </c>
       <c r="O21">
-        <v>0.341913384</v>
+        <v>0.3414667199999999</v>
       </c>
       <c r="P21">
-        <v>0.7977978960000001</v>
+        <v>0.79675568</v>
       </c>
       <c r="Q21">
-        <v>0.7897978960000001</v>
+        <v>0.78875568</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1840198764367923</v>
+        <v>0.1853024044525101</v>
       </c>
       <c r="T21">
-        <v>0.9637301483934649</v>
+        <v>0.9726725013080386</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>41.28854186403627</v>
+        <v>39.22411477083445</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1552839235620081</v>
+        <v>0.1548218472102145</v>
       </c>
       <c r="C22">
-        <v>2.70704193705084</v>
+        <v>2.69083964368961</v>
       </c>
       <c r="D22">
-        <v>3.16104193705084</v>
+        <v>3.17443964368961</v>
       </c>
       <c r="E22">
-        <v>-0.4580000000000001</v>
+        <v>-0.4284</v>
       </c>
       <c r="F22">
-        <v>0.592</v>
+        <v>0.6216</v>
       </c>
       <c r="G22">
         <v>0.138</v>
@@ -3085,28 +3085,28 @@
         <v>1.168</v>
       </c>
       <c r="M22">
-        <v>0.0297776</v>
+        <v>0.03126648</v>
       </c>
       <c r="N22">
-        <v>1.1382224</v>
+        <v>1.13673352</v>
       </c>
       <c r="O22">
-        <v>0.3414667199999999</v>
+        <v>0.341020056</v>
       </c>
       <c r="P22">
-        <v>0.79675568</v>
+        <v>0.795713464</v>
       </c>
       <c r="Q22">
-        <v>0.78875568</v>
+        <v>0.787713464</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1853024044525101</v>
+        <v>0.1866174015319171</v>
       </c>
       <c r="T22">
-        <v>0.9726725013080386</v>
+        <v>0.9818412429039938</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>39.22411477083445</v>
+        <v>37.3562997817471</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1548218472102144</v>
+        <v>0.1543597708584208</v>
       </c>
       <c r="C23">
-        <v>2.69083964368961</v>
+        <v>2.67475140295316</v>
       </c>
       <c r="D23">
-        <v>3.17443964368961</v>
+        <v>3.18795140295316</v>
       </c>
       <c r="E23">
-        <v>-0.4284000000000001</v>
+        <v>-0.3988</v>
       </c>
       <c r="F23">
-        <v>0.6215999999999999</v>
+        <v>0.6512</v>
       </c>
       <c r="G23">
         <v>0.138</v>
@@ -3167,28 +3167,28 @@
         <v>1.168</v>
       </c>
       <c r="M23">
-        <v>0.03126647999999999</v>
+        <v>0.03275536</v>
       </c>
       <c r="N23">
-        <v>1.13673352</v>
+        <v>1.13524464</v>
       </c>
       <c r="O23">
-        <v>0.341020056</v>
+        <v>0.340573392</v>
       </c>
       <c r="P23">
-        <v>0.795713464</v>
+        <v>0.794671248</v>
       </c>
       <c r="Q23">
-        <v>0.787713464</v>
+        <v>0.786671248</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.186617401531917</v>
+        <v>0.1879661164851549</v>
       </c>
       <c r="T23">
-        <v>0.9818412429039937</v>
+        <v>0.9912450804383066</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>37.3562997817471</v>
+        <v>35.65828615530405</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1543597708584208</v>
+        <v>0.1538976945066272</v>
       </c>
       <c r="C24">
-        <v>2.67475140295316</v>
+        <v>2.658778677435704</v>
       </c>
       <c r="D24">
-        <v>3.18795140295316</v>
+        <v>3.201578677435704</v>
       </c>
       <c r="E24">
-        <v>-0.3988</v>
+        <v>-0.3692</v>
       </c>
       <c r="F24">
-        <v>0.6512</v>
+        <v>0.6808000000000001</v>
       </c>
       <c r="G24">
         <v>0.138</v>
@@ -3249,28 +3249,28 @@
         <v>1.168</v>
       </c>
       <c r="M24">
-        <v>0.03275536</v>
+        <v>0.03424424</v>
       </c>
       <c r="N24">
-        <v>1.13524464</v>
+        <v>1.13375576</v>
       </c>
       <c r="O24">
-        <v>0.340573392</v>
+        <v>0.3401267279999999</v>
       </c>
       <c r="P24">
-        <v>0.794671248</v>
+        <v>0.7936290319999999</v>
       </c>
       <c r="Q24">
-        <v>0.786671248</v>
+        <v>0.7856290319999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1879661164851549</v>
+        <v>0.1893498629956197</v>
       </c>
       <c r="T24">
-        <v>0.9912450804383066</v>
+        <v>1.000893173492991</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>35.65828615530405</v>
+        <v>34.10792588768213</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1538976945066272</v>
+        <v>0.1534356181548335</v>
       </c>
       <c r="C25">
-        <v>2.658778677435704</v>
+        <v>2.64292295484694</v>
       </c>
       <c r="D25">
-        <v>3.201578677435704</v>
+        <v>3.21532295484694</v>
       </c>
       <c r="E25">
-        <v>-0.3692</v>
+        <v>-0.3396</v>
       </c>
       <c r="F25">
-        <v>0.6808000000000001</v>
+        <v>0.7104</v>
       </c>
       <c r="G25">
         <v>0.138</v>
@@ -3331,28 +3331,28 @@
         <v>1.168</v>
       </c>
       <c r="M25">
-        <v>0.03424424</v>
+        <v>0.03573312</v>
       </c>
       <c r="N25">
-        <v>1.13375576</v>
+        <v>1.13226688</v>
       </c>
       <c r="O25">
-        <v>0.3401267279999999</v>
+        <v>0.339680064</v>
       </c>
       <c r="P25">
-        <v>0.7936290319999999</v>
+        <v>0.792586816</v>
       </c>
       <c r="Q25">
-        <v>0.7856290319999999</v>
+        <v>0.784586816</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1893498629956197</v>
+        <v>0.1907700238879388</v>
       </c>
       <c r="T25">
-        <v>1.000893173492991</v>
+        <v>1.010795163733326</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>34.10792588768213</v>
+        <v>32.68676230902871</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1534356181548335</v>
+        <v>0.1529735418030399</v>
       </c>
       <c r="C26">
-        <v>2.64292295484694</v>
+        <v>2.627185748553473</v>
       </c>
       <c r="D26">
-        <v>3.21532295484694</v>
+        <v>3.229185748553473</v>
       </c>
       <c r="E26">
-        <v>-0.3396000000000001</v>
+        <v>-0.3100000000000001</v>
       </c>
       <c r="F26">
-        <v>0.7103999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="G26">
         <v>0.138</v>
@@ -3413,28 +3413,28 @@
         <v>1.168</v>
       </c>
       <c r="M26">
-        <v>0.03573311999999999</v>
+        <v>0.037222</v>
       </c>
       <c r="N26">
-        <v>1.13226688</v>
+        <v>1.130778</v>
       </c>
       <c r="O26">
-        <v>0.339680064</v>
+        <v>0.3392334</v>
       </c>
       <c r="P26">
-        <v>0.792586816</v>
+        <v>0.7915445999999999</v>
       </c>
       <c r="Q26">
-        <v>0.784586816</v>
+        <v>0.7835445999999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1907700238879388</v>
+        <v>0.1922280557373865</v>
       </c>
       <c r="T26">
-        <v>1.010795163733326</v>
+        <v>1.020961207046736</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>32.68676230902872</v>
+        <v>31.37929181666756</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1529735418030399</v>
+        <v>0.1525114654512462</v>
       </c>
       <c r="C27">
-        <v>2.627185748553473</v>
+        <v>2.611568598134311</v>
       </c>
       <c r="D27">
-        <v>3.229185748553473</v>
+        <v>3.243168598134311</v>
       </c>
       <c r="E27">
-        <v>-0.3100000000000001</v>
+        <v>-0.2804</v>
       </c>
       <c r="F27">
-        <v>0.74</v>
+        <v>0.7696000000000001</v>
       </c>
       <c r="G27">
         <v>0.138</v>
@@ -3495,28 +3495,28 @@
         <v>1.168</v>
       </c>
       <c r="M27">
-        <v>0.037222</v>
+        <v>0.03871088</v>
       </c>
       <c r="N27">
-        <v>1.130778</v>
+        <v>1.12928912</v>
       </c>
       <c r="O27">
-        <v>0.3392334</v>
+        <v>0.338786736</v>
       </c>
       <c r="P27">
-        <v>0.7915445999999999</v>
+        <v>0.7905023839999999</v>
       </c>
       <c r="Q27">
-        <v>0.7835445999999999</v>
+        <v>0.7825023839999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1922280557373865</v>
+        <v>0.1937254938530354</v>
       </c>
       <c r="T27">
-        <v>1.020961207046736</v>
+        <v>1.031402008287535</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>31.37929181666756</v>
+        <v>30.17239597756496</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1525114654512462</v>
+        <v>0.1520493890994526</v>
       </c>
       <c r="C28">
-        <v>2.611568598134311</v>
+        <v>2.596073069950849</v>
       </c>
       <c r="D28">
-        <v>3.243168598134311</v>
+        <v>3.257273069950849</v>
       </c>
       <c r="E28">
-        <v>-0.2804</v>
+        <v>-0.2508</v>
       </c>
       <c r="F28">
-        <v>0.7696000000000001</v>
+        <v>0.7992</v>
       </c>
       <c r="G28">
         <v>0.138</v>
@@ -3577,28 +3577,28 @@
         <v>1.168</v>
       </c>
       <c r="M28">
-        <v>0.03871088</v>
+        <v>0.04019976</v>
       </c>
       <c r="N28">
-        <v>1.12928912</v>
+        <v>1.12780024</v>
       </c>
       <c r="O28">
-        <v>0.338786736</v>
+        <v>0.338340072</v>
       </c>
       <c r="P28">
-        <v>0.7905023839999999</v>
+        <v>0.789460168</v>
       </c>
       <c r="Q28">
-        <v>0.7825023839999999</v>
+        <v>0.781460168</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1937254938530354</v>
+        <v>0.195263957670483</v>
       </c>
       <c r="T28">
-        <v>1.031402008287535</v>
+        <v>1.042128858877397</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>30.17239597756496</v>
+        <v>29.05489983024774</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1520493890994526</v>
+        <v>0.1515873127476589</v>
       </c>
       <c r="C29">
-        <v>2.596073069950849</v>
+        <v>2.580700757731792</v>
       </c>
       <c r="D29">
-        <v>3.257273069950849</v>
+        <v>3.271500757731792</v>
       </c>
       <c r="E29">
-        <v>-0.2508</v>
+        <v>-0.2212</v>
       </c>
       <c r="F29">
-        <v>0.7992</v>
+        <v>0.8288000000000001</v>
       </c>
       <c r="G29">
         <v>0.138</v>
@@ -3659,28 +3659,28 @@
         <v>1.168</v>
       </c>
       <c r="M29">
-        <v>0.04019976</v>
+        <v>0.04168864000000001</v>
       </c>
       <c r="N29">
-        <v>1.12780024</v>
+        <v>1.12631136</v>
       </c>
       <c r="O29">
-        <v>0.338340072</v>
+        <v>0.337893408</v>
       </c>
       <c r="P29">
-        <v>0.789460168</v>
+        <v>0.7884179519999999</v>
       </c>
       <c r="Q29">
-        <v>0.781460168</v>
+        <v>0.7804179519999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.195263957670483</v>
+        <v>0.1968451565939708</v>
       </c>
       <c r="T29">
-        <v>1.042128858877397</v>
+        <v>1.0531536775392</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>29.05489983024774</v>
+        <v>28.01722483631032</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1515873127476589</v>
+        <v>0.1511252363958653</v>
       </c>
       <c r="C30">
-        <v>2.580700757731792</v>
+        <v>2.565453283173473</v>
       </c>
       <c r="D30">
-        <v>3.271500757731792</v>
+        <v>3.285853283173473</v>
       </c>
       <c r="E30">
-        <v>-0.2212</v>
+        <v>-0.1916</v>
       </c>
       <c r="F30">
-        <v>0.8288000000000001</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="G30">
         <v>0.138</v>
@@ -3741,28 +3741,28 @@
         <v>1.168</v>
       </c>
       <c r="M30">
-        <v>0.04168864000000001</v>
+        <v>0.04317752</v>
       </c>
       <c r="N30">
-        <v>1.12631136</v>
+        <v>1.12482248</v>
       </c>
       <c r="O30">
-        <v>0.337893408</v>
+        <v>0.337446744</v>
       </c>
       <c r="P30">
-        <v>0.7884179519999999</v>
+        <v>0.787375736</v>
       </c>
       <c r="Q30">
-        <v>0.7804179519999999</v>
+        <v>0.779375736</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1968451565939708</v>
+        <v>0.1984708963322047</v>
       </c>
       <c r="T30">
-        <v>1.0531536775392</v>
+        <v>1.064489054473167</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>28.01722483631032</v>
+        <v>27.05111363505824</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1511252363958653</v>
+        <v>0.1506631600440717</v>
       </c>
       <c r="C31">
-        <v>2.565453283173473</v>
+        <v>2.550332296556056</v>
       </c>
       <c r="D31">
-        <v>3.285853283173473</v>
+        <v>3.300332296556056</v>
       </c>
       <c r="E31">
-        <v>-0.1916000000000001</v>
+        <v>-0.162</v>
       </c>
       <c r="F31">
-        <v>0.8583999999999999</v>
+        <v>0.888</v>
       </c>
       <c r="G31">
         <v>0.138</v>
@@ -3823,28 +3823,28 @@
         <v>1.168</v>
       </c>
       <c r="M31">
-        <v>0.04317752</v>
+        <v>0.04466639999999999</v>
       </c>
       <c r="N31">
-        <v>1.12482248</v>
+        <v>1.1233336</v>
       </c>
       <c r="O31">
-        <v>0.337446744</v>
+        <v>0.33700008</v>
       </c>
       <c r="P31">
-        <v>0.787375736</v>
+        <v>0.7863335200000001</v>
       </c>
       <c r="Q31">
-        <v>0.779375736</v>
+        <v>0.7783335200000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1984708963322047</v>
+        <v>0.2001430857772453</v>
       </c>
       <c r="T31">
-        <v>1.064489054473167</v>
+        <v>1.076148299319532</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>27.05111363505824</v>
+        <v>26.14940984722297</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1506631600440717</v>
+        <v>0.150201083692278</v>
       </c>
       <c r="C32">
-        <v>2.550332296556056</v>
+        <v>2.535339477376078</v>
       </c>
       <c r="D32">
-        <v>3.300332296556056</v>
+        <v>3.314939477376078</v>
       </c>
       <c r="E32">
-        <v>-0.162</v>
+        <v>-0.1324000000000001</v>
       </c>
       <c r="F32">
-        <v>0.888</v>
+        <v>0.9176</v>
       </c>
       <c r="G32">
         <v>0.138</v>
@@ -3905,28 +3905,28 @@
         <v>1.168</v>
       </c>
       <c r="M32">
-        <v>0.04466639999999999</v>
+        <v>0.04615527999999999</v>
       </c>
       <c r="N32">
-        <v>1.1233336</v>
+        <v>1.12184472</v>
       </c>
       <c r="O32">
-        <v>0.33700008</v>
+        <v>0.3365534159999999</v>
       </c>
       <c r="P32">
-        <v>0.7863335200000001</v>
+        <v>0.785291304</v>
       </c>
       <c r="Q32">
-        <v>0.7783335200000001</v>
+        <v>0.777291304</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2001430857772453</v>
+        <v>0.2018637444815624</v>
       </c>
       <c r="T32">
-        <v>1.076148299319532</v>
+        <v>1.088145493291879</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>26.14940984722297</v>
+        <v>25.30588049731255</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.150201083692278</v>
+        <v>0.1497390073404844</v>
       </c>
       <c r="C33">
-        <v>2.535339477376078</v>
+        <v>2.520476534995888</v>
       </c>
       <c r="D33">
-        <v>3.314939477376078</v>
+        <v>3.329676534995889</v>
       </c>
       <c r="E33">
-        <v>-0.1324000000000001</v>
+        <v>-0.1028</v>
       </c>
       <c r="F33">
-        <v>0.9176</v>
+        <v>0.9472</v>
       </c>
       <c r="G33">
         <v>0.138</v>
@@ -3987,28 +3987,28 @@
         <v>1.168</v>
       </c>
       <c r="M33">
-        <v>0.04615527999999999</v>
+        <v>0.04764416</v>
       </c>
       <c r="N33">
-        <v>1.12184472</v>
+        <v>1.12035584</v>
       </c>
       <c r="O33">
-        <v>0.3365534159999999</v>
+        <v>0.336106752</v>
       </c>
       <c r="P33">
-        <v>0.785291304</v>
+        <v>0.7842490879999999</v>
       </c>
       <c r="Q33">
-        <v>0.777291304</v>
+        <v>0.7762490879999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2018637444815624</v>
+        <v>0.20363501079483</v>
       </c>
       <c r="T33">
-        <v>1.088145493291879</v>
+        <v>1.100495545910472</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>25.30588049731255</v>
+        <v>24.51507173177153</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1497390073404844</v>
+        <v>0.1492769309886907</v>
       </c>
       <c r="C34">
-        <v>2.520476534995888</v>
+        <v>2.505745209310476</v>
       </c>
       <c r="D34">
-        <v>3.329676534995889</v>
+        <v>3.344545209310476</v>
       </c>
       <c r="E34">
-        <v>-0.1028</v>
+        <v>-0.07320000000000004</v>
       </c>
       <c r="F34">
-        <v>0.9472</v>
+        <v>0.9768</v>
       </c>
       <c r="G34">
         <v>0.138</v>
@@ -4069,28 +4069,28 @@
         <v>1.168</v>
       </c>
       <c r="M34">
-        <v>0.04764416</v>
+        <v>0.04913304</v>
       </c>
       <c r="N34">
-        <v>1.12035584</v>
+        <v>1.11886696</v>
       </c>
       <c r="O34">
-        <v>0.336106752</v>
+        <v>0.335660088</v>
       </c>
       <c r="P34">
-        <v>0.7842490879999999</v>
+        <v>0.7832068719999998</v>
       </c>
       <c r="Q34">
-        <v>0.7762490879999999</v>
+        <v>0.7752068719999998</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.20363501079483</v>
+        <v>0.2054591507293892</v>
       </c>
       <c r="T34">
-        <v>1.100495545910472</v>
+        <v>1.113214256816186</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>24.51507173177153</v>
+        <v>23.7721907702027</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1492769309886907</v>
+        <v>0.1488148546368971</v>
       </c>
       <c r="C35">
-        <v>2.505745209310476</v>
+        <v>2.491147271432238</v>
       </c>
       <c r="D35">
-        <v>3.344545209310476</v>
+        <v>3.359547271432238</v>
       </c>
       <c r="E35">
-        <v>-0.07320000000000004</v>
+        <v>-0.04360000000000008</v>
       </c>
       <c r="F35">
-        <v>0.9768</v>
+        <v>1.0064</v>
       </c>
       <c r="G35">
         <v>0.138</v>
@@ -4151,28 +4151,28 @@
         <v>1.168</v>
       </c>
       <c r="M35">
-        <v>0.04913304</v>
+        <v>0.05062191999999999</v>
       </c>
       <c r="N35">
-        <v>1.11886696</v>
+        <v>1.11737808</v>
       </c>
       <c r="O35">
-        <v>0.335660088</v>
+        <v>0.335213424</v>
       </c>
       <c r="P35">
-        <v>0.7832068719999998</v>
+        <v>0.782164656</v>
       </c>
       <c r="Q35">
-        <v>0.7752068719999998</v>
+        <v>0.774164656</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2054591507293892</v>
+        <v>0.2073385676316623</v>
       </c>
       <c r="T35">
-        <v>1.113214256816186</v>
+        <v>1.126318383203893</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>23.7721907702027</v>
+        <v>23.07300868872615</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1488148546368971</v>
+        <v>0.1483527782851034</v>
       </c>
       <c r="C36">
-        <v>2.491147271432238</v>
+        <v>2.476684524394281</v>
       </c>
       <c r="D36">
-        <v>3.359547271432238</v>
+        <v>3.374684524394281</v>
       </c>
       <c r="E36">
-        <v>-0.04360000000000008</v>
+        <v>-0.01400000000000001</v>
       </c>
       <c r="F36">
-        <v>1.0064</v>
+        <v>1.036</v>
       </c>
       <c r="G36">
         <v>0.138</v>
@@ -4233,28 +4233,28 @@
         <v>1.168</v>
       </c>
       <c r="M36">
-        <v>0.05062191999999999</v>
+        <v>0.0521108</v>
       </c>
       <c r="N36">
-        <v>1.11737808</v>
+        <v>1.1158892</v>
       </c>
       <c r="O36">
-        <v>0.335213424</v>
+        <v>0.33476676</v>
       </c>
       <c r="P36">
-        <v>0.782164656</v>
+        <v>0.7811224400000001</v>
       </c>
       <c r="Q36">
-        <v>0.774164656</v>
+        <v>0.7731224400000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2073385676316623</v>
+        <v>0.209275812746313</v>
       </c>
       <c r="T36">
-        <v>1.126318383203893</v>
+        <v>1.139825713480451</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>23.07300868872615</v>
+        <v>22.41377986904826</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1483527782851034</v>
+        <v>0.1478907019333098</v>
       </c>
       <c r="C37">
-        <v>2.476684524394281</v>
+        <v>2.462358803872788</v>
       </c>
       <c r="D37">
-        <v>3.374684524394281</v>
+        <v>3.389958803872788</v>
       </c>
       <c r="E37">
-        <v>-0.01400000000000001</v>
+        <v>0.01560000000000006</v>
       </c>
       <c r="F37">
-        <v>1.036</v>
+        <v>1.0656</v>
       </c>
       <c r="G37">
         <v>0.138</v>
@@ -4315,28 +4315,28 @@
         <v>1.168</v>
       </c>
       <c r="M37">
-        <v>0.0521108</v>
+        <v>0.05359968</v>
       </c>
       <c r="N37">
-        <v>1.1158892</v>
+        <v>1.11440032</v>
       </c>
       <c r="O37">
-        <v>0.33476676</v>
+        <v>0.334320096</v>
       </c>
       <c r="P37">
-        <v>0.7811224400000001</v>
+        <v>0.780080224</v>
       </c>
       <c r="Q37">
-        <v>0.7731224400000001</v>
+        <v>0.772080224</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.209275812746313</v>
+        <v>0.2112735967707966</v>
       </c>
       <c r="T37">
-        <v>1.139825713480451</v>
+        <v>1.153755147828152</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>22.41377986904826</v>
+        <v>21.7911748726858</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1478907019333098</v>
+        <v>0.1474286255815162</v>
       </c>
       <c r="C38">
-        <v>2.462358803872787</v>
+        <v>2.448171978929139</v>
       </c>
       <c r="D38">
-        <v>3.389958803872787</v>
+        <v>3.405371978929139</v>
       </c>
       <c r="E38">
-        <v>0.01559999999999984</v>
+        <v>0.04519999999999991</v>
       </c>
       <c r="F38">
-        <v>1.0656</v>
+        <v>1.0952</v>
       </c>
       <c r="G38">
         <v>0.138</v>
@@ -4397,28 +4397,28 @@
         <v>1.168</v>
       </c>
       <c r="M38">
-        <v>0.05359967999999999</v>
+        <v>0.05508855999999999</v>
       </c>
       <c r="N38">
-        <v>1.11440032</v>
+        <v>1.11291144</v>
       </c>
       <c r="O38">
-        <v>0.334320096</v>
+        <v>0.333873432</v>
       </c>
       <c r="P38">
-        <v>0.780080224</v>
+        <v>0.779038008</v>
       </c>
       <c r="Q38">
-        <v>0.772080224</v>
+        <v>0.771038008</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2112735967707966</v>
+        <v>0.2133348025103431</v>
       </c>
       <c r="T38">
-        <v>1.153755147828152</v>
+        <v>1.16812678644086</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>21.79117487268581</v>
+        <v>21.20222420045106</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1474286255815162</v>
+        <v>0.1469665492297225</v>
       </c>
       <c r="C39">
-        <v>2.448171978929139</v>
+        <v>2.434125952772319</v>
       </c>
       <c r="D39">
-        <v>3.405371978929139</v>
+        <v>3.420925952772319</v>
       </c>
       <c r="E39">
-        <v>0.04519999999999991</v>
+        <v>0.07479999999999998</v>
       </c>
       <c r="F39">
-        <v>1.0952</v>
+        <v>1.1248</v>
       </c>
       <c r="G39">
         <v>0.138</v>
@@ -4479,28 +4479,28 @@
         <v>1.168</v>
       </c>
       <c r="M39">
-        <v>0.05508855999999999</v>
+        <v>0.05657744</v>
       </c>
       <c r="N39">
-        <v>1.11291144</v>
+        <v>1.11142256</v>
       </c>
       <c r="O39">
-        <v>0.333873432</v>
+        <v>0.3334267679999999</v>
       </c>
       <c r="P39">
-        <v>0.779038008</v>
+        <v>0.7779957919999999</v>
       </c>
       <c r="Q39">
-        <v>0.771038008</v>
+        <v>0.7699957919999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2133348025103431</v>
+        <v>0.215462498757617</v>
       </c>
       <c r="T39">
-        <v>1.16812678644086</v>
+        <v>1.182962026299138</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>21.20222420045106</v>
+        <v>20.64427093201813</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1469665492297225</v>
+        <v>0.1465044728779289</v>
       </c>
       <c r="C40">
-        <v>2.434125952772319</v>
+        <v>2.42022266354235</v>
       </c>
       <c r="D40">
-        <v>3.420925952772319</v>
+        <v>3.43662266354235</v>
       </c>
       <c r="E40">
-        <v>0.07479999999999998</v>
+        <v>0.1044</v>
       </c>
       <c r="F40">
-        <v>1.1248</v>
+        <v>1.1544</v>
       </c>
       <c r="G40">
         <v>0.138</v>
@@ -4561,28 +4561,28 @@
         <v>1.168</v>
       </c>
       <c r="M40">
-        <v>0.05657744</v>
+        <v>0.05806632</v>
       </c>
       <c r="N40">
-        <v>1.11142256</v>
+        <v>1.10993368</v>
       </c>
       <c r="O40">
-        <v>0.3334267679999999</v>
+        <v>0.3329801039999999</v>
       </c>
       <c r="P40">
-        <v>0.7779957919999999</v>
+        <v>0.7769535759999999</v>
       </c>
       <c r="Q40">
-        <v>0.7699957919999999</v>
+        <v>0.7689535759999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.215462498757617</v>
+        <v>0.2176599555375883</v>
       </c>
       <c r="T40">
-        <v>1.182962026299138</v>
+        <v>1.198283667464246</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>20.64427093201813</v>
+        <v>20.11493065170997</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1465044728779289</v>
+        <v>0.1460423965261353</v>
       </c>
       <c r="C41">
-        <v>2.42022266354235</v>
+        <v>2.406464085115376</v>
       </c>
       <c r="D41">
-        <v>3.43662266354235</v>
+        <v>3.452464085115376</v>
       </c>
       <c r="E41">
-        <v>0.1044</v>
+        <v>0.1339999999999999</v>
       </c>
       <c r="F41">
-        <v>1.1544</v>
+        <v>1.184</v>
       </c>
       <c r="G41">
         <v>0.138</v>
@@ -4643,28 +4643,28 @@
         <v>1.168</v>
       </c>
       <c r="M41">
-        <v>0.05806632</v>
+        <v>0.0595552</v>
       </c>
       <c r="N41">
-        <v>1.10993368</v>
+        <v>1.1084448</v>
       </c>
       <c r="O41">
-        <v>0.3329801039999999</v>
+        <v>0.33253344</v>
       </c>
       <c r="P41">
-        <v>0.7769535759999999</v>
+        <v>0.77591136</v>
       </c>
       <c r="Q41">
-        <v>0.7689535759999999</v>
+        <v>0.76791136</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2176599555375883</v>
+        <v>0.2199306608768921</v>
       </c>
       <c r="T41">
-        <v>1.198283667464246</v>
+        <v>1.214116030001523</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>20.11493065170997</v>
+        <v>19.61205738541723</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1460423965261353</v>
+        <v>0.1455803201743416</v>
       </c>
       <c r="C42">
-        <v>2.406464085115376</v>
+        <v>2.392852227931127</v>
       </c>
       <c r="D42">
-        <v>3.452464085115376</v>
+        <v>3.468452227931127</v>
       </c>
       <c r="E42">
-        <v>0.1339999999999999</v>
+        <v>0.1636</v>
       </c>
       <c r="F42">
-        <v>1.184</v>
+        <v>1.2136</v>
       </c>
       <c r="G42">
         <v>0.138</v>
@@ -4725,28 +4725,28 @@
         <v>1.168</v>
       </c>
       <c r="M42">
-        <v>0.0595552</v>
+        <v>0.06104408</v>
       </c>
       <c r="N42">
-        <v>1.1084448</v>
+        <v>1.10695592</v>
       </c>
       <c r="O42">
-        <v>0.33253344</v>
+        <v>0.332086776</v>
       </c>
       <c r="P42">
-        <v>0.77591136</v>
+        <v>0.774869144</v>
       </c>
       <c r="Q42">
-        <v>0.76791136</v>
+        <v>0.7668691439999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2199306608768921</v>
+        <v>0.2222783392785451</v>
       </c>
       <c r="T42">
-        <v>1.214116030001523</v>
+        <v>1.230485082794302</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>19.61205738541723</v>
+        <v>19.13371452235827</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1455803201743416</v>
+        <v>0.145118243822548</v>
       </c>
       <c r="C43">
-        <v>2.392852227931127</v>
+        <v>2.379389139843468</v>
       </c>
       <c r="D43">
-        <v>3.468452227931127</v>
+        <v>3.484589139843468</v>
       </c>
       <c r="E43">
-        <v>0.1636</v>
+        <v>0.1932</v>
       </c>
       <c r="F43">
-        <v>1.2136</v>
+        <v>1.2432</v>
       </c>
       <c r="G43">
         <v>0.138</v>
@@ -4807,28 +4807,28 @@
         <v>1.168</v>
       </c>
       <c r="M43">
-        <v>0.06104408</v>
+        <v>0.06253296</v>
       </c>
       <c r="N43">
-        <v>1.10695592</v>
+        <v>1.10546704</v>
       </c>
       <c r="O43">
-        <v>0.332086776</v>
+        <v>0.331640112</v>
       </c>
       <c r="P43">
-        <v>0.774869144</v>
+        <v>0.773826928</v>
       </c>
       <c r="Q43">
-        <v>0.7668691439999999</v>
+        <v>0.765826928</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2222783392785451</v>
+        <v>0.2247069721078413</v>
       </c>
       <c r="T43">
-        <v>1.230485082794302</v>
+        <v>1.247418585683383</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>19.13371452235827</v>
+        <v>18.67814989087355</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.145118243822548</v>
+        <v>0.1446561674707543</v>
       </c>
       <c r="C44">
-        <v>2.379389139843468</v>
+        <v>2.36607690699482</v>
       </c>
       <c r="D44">
-        <v>3.484589139843468</v>
+        <v>3.50087690699482</v>
       </c>
       <c r="E44">
-        <v>0.1931999999999998</v>
+        <v>0.2227999999999999</v>
       </c>
       <c r="F44">
-        <v>1.2432</v>
+        <v>1.2728</v>
       </c>
       <c r="G44">
         <v>0.138</v>
@@ -4889,28 +4889,28 @@
         <v>1.168</v>
       </c>
       <c r="M44">
-        <v>0.06253295999999998</v>
+        <v>0.06402184</v>
       </c>
       <c r="N44">
-        <v>1.10546704</v>
+        <v>1.10397816</v>
       </c>
       <c r="O44">
-        <v>0.331640112</v>
+        <v>0.331193448</v>
       </c>
       <c r="P44">
-        <v>0.773826928</v>
+        <v>0.772784712</v>
       </c>
       <c r="Q44">
-        <v>0.765826928</v>
+        <v>0.764784712</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2247069721078413</v>
+        <v>0.2272208201241303</v>
       </c>
       <c r="T44">
-        <v>1.247418585683383</v>
+        <v>1.264946246568573</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>18.67814989087355</v>
+        <v>18.24377431201603</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1446561674707543</v>
+        <v>0.1441940911189606</v>
       </c>
       <c r="C45">
-        <v>2.36607690699482</v>
+        <v>2.352917654715199</v>
       </c>
       <c r="D45">
-        <v>3.50087690699482</v>
+        <v>3.517317654715199</v>
       </c>
       <c r="E45">
-        <v>0.2227999999999999</v>
+        <v>0.2524</v>
       </c>
       <c r="F45">
-        <v>1.2728</v>
+        <v>1.3024</v>
       </c>
       <c r="G45">
         <v>0.138</v>
@@ -4971,28 +4971,28 @@
         <v>1.168</v>
       </c>
       <c r="M45">
-        <v>0.06402184</v>
+        <v>0.06551071999999999</v>
       </c>
       <c r="N45">
-        <v>1.10397816</v>
+        <v>1.10248928</v>
       </c>
       <c r="O45">
-        <v>0.331193448</v>
+        <v>0.330746784</v>
       </c>
       <c r="P45">
-        <v>0.772784712</v>
+        <v>0.7717424959999999</v>
       </c>
       <c r="Q45">
-        <v>0.764784712</v>
+        <v>0.7637424959999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2272208201241303</v>
+        <v>0.2298244484267155</v>
       </c>
       <c r="T45">
-        <v>1.264946246568573</v>
+        <v>1.283099895342519</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>18.24377431201603</v>
+        <v>17.82914307765202</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1441940911189606</v>
+        <v>0.143732014767167</v>
       </c>
       <c r="C46">
-        <v>2.352917654715199</v>
+        <v>2.339913548446724</v>
       </c>
       <c r="D46">
-        <v>3.517317654715199</v>
+        <v>3.533913548446724</v>
       </c>
       <c r="E46">
-        <v>0.2524</v>
+        <v>0.282</v>
       </c>
       <c r="F46">
-        <v>1.3024</v>
+        <v>1.332</v>
       </c>
       <c r="G46">
         <v>0.138</v>
@@ -5053,28 +5053,28 @@
         <v>1.168</v>
       </c>
       <c r="M46">
-        <v>0.06551071999999999</v>
+        <v>0.06699960000000001</v>
       </c>
       <c r="N46">
-        <v>1.10248928</v>
+        <v>1.1010004</v>
       </c>
       <c r="O46">
-        <v>0.330746784</v>
+        <v>0.33030012</v>
       </c>
       <c r="P46">
-        <v>0.7717424959999999</v>
+        <v>0.77070028</v>
       </c>
       <c r="Q46">
-        <v>0.7637424959999999</v>
+        <v>0.76270028</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2298244484267155</v>
+        <v>0.2325227541221219</v>
       </c>
       <c r="T46">
-        <v>1.283099895342519</v>
+        <v>1.301913676799154</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>17.82914307765202</v>
+        <v>17.43293989814864</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.143732014767167</v>
+        <v>0.1432699384153734</v>
       </c>
       <c r="C47">
-        <v>2.339913548446724</v>
+        <v>2.327066794694419</v>
       </c>
       <c r="D47">
-        <v>3.533913548446724</v>
+        <v>3.550666794694419</v>
       </c>
       <c r="E47">
-        <v>0.282</v>
+        <v>0.3116000000000001</v>
       </c>
       <c r="F47">
-        <v>1.332</v>
+        <v>1.3616</v>
       </c>
       <c r="G47">
         <v>0.138</v>
@@ -5135,28 +5135,28 @@
         <v>1.168</v>
       </c>
       <c r="M47">
-        <v>0.06699960000000001</v>
+        <v>0.06848848</v>
       </c>
       <c r="N47">
-        <v>1.1010004</v>
+        <v>1.09951152</v>
       </c>
       <c r="O47">
-        <v>0.33030012</v>
+        <v>0.3298534559999999</v>
       </c>
       <c r="P47">
-        <v>0.77070028</v>
+        <v>0.7696580639999999</v>
       </c>
       <c r="Q47">
-        <v>0.76270028</v>
+        <v>0.7616580639999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2325227541221219</v>
+        <v>0.2353209970655062</v>
       </c>
       <c r="T47">
-        <v>1.301913676799154</v>
+        <v>1.321424264976405</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>17.43293989814864</v>
+        <v>17.05396294384106</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1432699384153734</v>
+        <v>0.1428078620635797</v>
       </c>
       <c r="C48">
-        <v>2.327066794694419</v>
+        <v>2.314379642004176</v>
       </c>
       <c r="D48">
-        <v>3.550666794694419</v>
+        <v>3.567579642004176</v>
       </c>
       <c r="E48">
-        <v>0.3116000000000001</v>
+        <v>0.3411999999999999</v>
       </c>
       <c r="F48">
-        <v>1.3616</v>
+        <v>1.3912</v>
       </c>
       <c r="G48">
         <v>0.138</v>
@@ -5217,28 +5217,28 @@
         <v>1.168</v>
       </c>
       <c r="M48">
-        <v>0.06848848</v>
+        <v>0.06997736</v>
       </c>
       <c r="N48">
-        <v>1.09951152</v>
+        <v>1.09802264</v>
       </c>
       <c r="O48">
-        <v>0.3298534559999999</v>
+        <v>0.3294067919999999</v>
       </c>
       <c r="P48">
-        <v>0.7696580639999999</v>
+        <v>0.768615848</v>
       </c>
       <c r="Q48">
-        <v>0.7616580639999999</v>
+        <v>0.760615848</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2353209970655062</v>
+        <v>0.2382248340822259</v>
       </c>
       <c r="T48">
-        <v>1.321424264976405</v>
+        <v>1.341671101764119</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>17.05396294384106</v>
+        <v>16.69111266844019</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1428078620635797</v>
+        <v>0.1423457857117861</v>
       </c>
       <c r="C49">
-        <v>2.314379642004176</v>
+        <v>2.301854381968815</v>
       </c>
       <c r="D49">
-        <v>3.567579642004176</v>
+        <v>3.584654381968816</v>
       </c>
       <c r="E49">
-        <v>0.3411999999999999</v>
+        <v>0.3708</v>
       </c>
       <c r="F49">
-        <v>1.3912</v>
+        <v>1.4208</v>
       </c>
       <c r="G49">
         <v>0.138</v>
@@ -5299,28 +5299,28 @@
         <v>1.168</v>
       </c>
       <c r="M49">
-        <v>0.06997736</v>
+        <v>0.07146624</v>
       </c>
       <c r="N49">
-        <v>1.09802264</v>
+        <v>1.09653376</v>
       </c>
       <c r="O49">
-        <v>0.3294067919999999</v>
+        <v>0.328960128</v>
       </c>
       <c r="P49">
-        <v>0.768615848</v>
+        <v>0.767573632</v>
       </c>
       <c r="Q49">
-        <v>0.760615848</v>
+        <v>0.7595736319999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2382248340822259</v>
+        <v>0.2412403571380502</v>
       </c>
       <c r="T49">
-        <v>1.341671101764119</v>
+        <v>1.362696663043668</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>16.69111266844019</v>
+        <v>16.34338115451435</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1423457857117861</v>
+        <v>0.1418837093599924</v>
       </c>
       <c r="C50">
-        <v>2.301854381968816</v>
+        <v>2.289493350263174</v>
       </c>
       <c r="D50">
-        <v>3.584654381968816</v>
+        <v>3.601893350263174</v>
       </c>
       <c r="E50">
-        <v>0.3707999999999998</v>
+        <v>0.4003999999999999</v>
       </c>
       <c r="F50">
-        <v>1.4208</v>
+        <v>1.4504</v>
       </c>
       <c r="G50">
         <v>0.138</v>
@@ -5381,28 +5381,28 @@
         <v>1.168</v>
       </c>
       <c r="M50">
-        <v>0.07146623999999999</v>
+        <v>0.07295512</v>
       </c>
       <c r="N50">
-        <v>1.09653376</v>
+        <v>1.09504488</v>
       </c>
       <c r="O50">
-        <v>0.328960128</v>
+        <v>0.328513464</v>
       </c>
       <c r="P50">
-        <v>0.767573632</v>
+        <v>0.7665314159999999</v>
       </c>
       <c r="Q50">
-        <v>0.7595736319999999</v>
+        <v>0.7585314159999998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2412403571380502</v>
+        <v>0.2443741359999852</v>
       </c>
       <c r="T50">
-        <v>1.362696663043668</v>
+        <v>1.384546756138101</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>16.34338115451436</v>
+        <v>16.0098427636059</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1418837093599924</v>
+        <v>0.1414216330081988</v>
       </c>
       <c r="C51">
-        <v>2.289493350263174</v>
+        <v>2.277298927709196</v>
       </c>
       <c r="D51">
-        <v>3.601893350263174</v>
+        <v>3.619298927709196</v>
       </c>
       <c r="E51">
-        <v>0.4003999999999999</v>
+        <v>0.4299999999999999</v>
       </c>
       <c r="F51">
-        <v>1.4504</v>
+        <v>1.48</v>
       </c>
       <c r="G51">
         <v>0.138</v>
@@ -5463,28 +5463,28 @@
         <v>1.168</v>
       </c>
       <c r="M51">
-        <v>0.07295512</v>
+        <v>0.074444</v>
       </c>
       <c r="N51">
-        <v>1.09504488</v>
+        <v>1.093556</v>
       </c>
       <c r="O51">
-        <v>0.328513464</v>
+        <v>0.3280668</v>
       </c>
       <c r="P51">
-        <v>0.7665314159999999</v>
+        <v>0.7654892</v>
       </c>
       <c r="Q51">
-        <v>0.7585314159999998</v>
+        <v>0.7574892</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2443741359999852</v>
+        <v>0.2476332660163976</v>
       </c>
       <c r="T51">
-        <v>1.384546756138101</v>
+        <v>1.407270852956311</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>16.0098427636059</v>
+        <v>15.68964590833378</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1414216330081988</v>
+        <v>0.1409595566564052</v>
       </c>
       <c r="C52">
-        <v>2.277298927709196</v>
+        <v>2.265273541372069</v>
       </c>
       <c r="D52">
-        <v>3.619298927709196</v>
+        <v>3.636873541372069</v>
       </c>
       <c r="E52">
-        <v>0.4299999999999999</v>
+        <v>0.4596</v>
       </c>
       <c r="F52">
-        <v>1.48</v>
+        <v>1.5096</v>
       </c>
       <c r="G52">
         <v>0.138</v>
@@ -5545,28 +5545,28 @@
         <v>1.168</v>
       </c>
       <c r="M52">
-        <v>0.074444</v>
+        <v>0.07593287999999999</v>
       </c>
       <c r="N52">
-        <v>1.093556</v>
+        <v>1.09206712</v>
       </c>
       <c r="O52">
-        <v>0.3280668</v>
+        <v>0.327620136</v>
       </c>
       <c r="P52">
-        <v>0.7654892</v>
+        <v>0.7644469839999999</v>
       </c>
       <c r="Q52">
-        <v>0.7574892</v>
+        <v>0.7564469839999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2476332660163976</v>
+        <v>0.2510254217477657</v>
       </c>
       <c r="T52">
-        <v>1.407270852956311</v>
+        <v>1.430922463930367</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>15.68964590833378</v>
+        <v>15.3820057924841</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1409595566564052</v>
+        <v>0.1404974803046115</v>
       </c>
       <c r="C53">
-        <v>2.265273541372069</v>
+        <v>2.253419665688432</v>
       </c>
       <c r="D53">
-        <v>3.636873541372069</v>
+        <v>3.654619665688433</v>
       </c>
       <c r="E53">
-        <v>0.4596</v>
+        <v>0.4892000000000001</v>
       </c>
       <c r="F53">
-        <v>1.5096</v>
+        <v>1.5392</v>
       </c>
       <c r="G53">
         <v>0.138</v>
@@ -5627,28 +5627,28 @@
         <v>1.168</v>
       </c>
       <c r="M53">
-        <v>0.07593287999999999</v>
+        <v>0.07742176000000001</v>
       </c>
       <c r="N53">
-        <v>1.09206712</v>
+        <v>1.09057824</v>
       </c>
       <c r="O53">
-        <v>0.327620136</v>
+        <v>0.327173472</v>
       </c>
       <c r="P53">
-        <v>0.7644469839999999</v>
+        <v>0.763404768</v>
       </c>
       <c r="Q53">
-        <v>0.7564469839999999</v>
+        <v>0.755404768</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2510254217477657</v>
+        <v>0.254558917301274</v>
       </c>
       <c r="T53">
-        <v>1.430922463930367</v>
+        <v>1.455559558695008</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>15.3820057924841</v>
+        <v>15.08619798878248</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1404974803046115</v>
+        <v>0.1400354039528179</v>
       </c>
       <c r="C54">
-        <v>2.253419665688432</v>
+        <v>2.241739823627801</v>
       </c>
       <c r="D54">
-        <v>3.654619665688433</v>
+        <v>3.672539823627801</v>
       </c>
       <c r="E54">
-        <v>0.4892000000000001</v>
+        <v>0.5187999999999999</v>
       </c>
       <c r="F54">
-        <v>1.5392</v>
+        <v>1.5688</v>
       </c>
       <c r="G54">
         <v>0.138</v>
@@ -5709,28 +5709,28 @@
         <v>1.168</v>
       </c>
       <c r="M54">
-        <v>0.07742176000000001</v>
+        <v>0.07891063999999999</v>
       </c>
       <c r="N54">
-        <v>1.09057824</v>
+        <v>1.08908936</v>
       </c>
       <c r="O54">
-        <v>0.327173472</v>
+        <v>0.326726808</v>
       </c>
       <c r="P54">
-        <v>0.763404768</v>
+        <v>0.762362552</v>
       </c>
       <c r="Q54">
-        <v>0.755404768</v>
+        <v>0.754362552</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.254558917301274</v>
+        <v>0.2582427743676976</v>
       </c>
       <c r="T54">
-        <v>1.455559558695008</v>
+        <v>1.481245040470911</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>15.08619798878248</v>
+        <v>14.80155274371112</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1400354039528179</v>
+        <v>0.1395733276010242</v>
       </c>
       <c r="C55">
-        <v>2.241739823627801</v>
+        <v>2.230236587888306</v>
       </c>
       <c r="D55">
-        <v>3.672539823627801</v>
+        <v>3.690636587888306</v>
       </c>
       <c r="E55">
-        <v>0.5187999999999999</v>
+        <v>0.5484</v>
       </c>
       <c r="F55">
-        <v>1.5688</v>
+        <v>1.5984</v>
       </c>
       <c r="G55">
         <v>0.138</v>
@@ -5791,28 +5791,28 @@
         <v>1.168</v>
       </c>
       <c r="M55">
-        <v>0.07891063999999999</v>
+        <v>0.08039952</v>
       </c>
       <c r="N55">
-        <v>1.08908936</v>
+        <v>1.08760048</v>
       </c>
       <c r="O55">
-        <v>0.326726808</v>
+        <v>0.3262801439999999</v>
       </c>
       <c r="P55">
-        <v>0.762362552</v>
+        <v>0.7613203359999999</v>
       </c>
       <c r="Q55">
-        <v>0.754362552</v>
+        <v>0.7533203359999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2582427743676976</v>
+        <v>0.2620867991326614</v>
       </c>
       <c r="T55">
-        <v>1.481245040470911</v>
+        <v>1.508047282324027</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>14.80155274371112</v>
+        <v>14.52744991512387</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1395733276010242</v>
+        <v>0.1391112512492306</v>
       </c>
       <c r="C56">
-        <v>2.230236587888306</v>
+        <v>2.218912582127976</v>
       </c>
       <c r="D56">
-        <v>3.690636587888306</v>
+        <v>3.708912582127977</v>
       </c>
       <c r="E56">
-        <v>0.5484</v>
+        <v>0.5780000000000001</v>
       </c>
       <c r="F56">
-        <v>1.5984</v>
+        <v>1.628</v>
       </c>
       <c r="G56">
         <v>0.138</v>
@@ -5873,28 +5873,28 @@
         <v>1.168</v>
       </c>
       <c r="M56">
-        <v>0.08039952</v>
+        <v>0.0818884</v>
       </c>
       <c r="N56">
-        <v>1.08760048</v>
+        <v>1.0861116</v>
       </c>
       <c r="O56">
-        <v>0.3262801439999999</v>
+        <v>0.32583348</v>
       </c>
       <c r="P56">
-        <v>0.7613203359999999</v>
+        <v>0.7602781199999999</v>
       </c>
       <c r="Q56">
-        <v>0.7533203359999999</v>
+        <v>0.7522781199999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2620867991326614</v>
+        <v>0.2661016694427347</v>
       </c>
       <c r="T56">
-        <v>1.508047282324027</v>
+        <v>1.53604073492617</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>14.52744991512387</v>
+        <v>14.26331446212162</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1391112512492306</v>
+        <v>0.1386491748974369</v>
       </c>
       <c r="C57">
-        <v>2.218912582127976</v>
+        <v>2.207770482232791</v>
       </c>
       <c r="D57">
-        <v>3.708912582127977</v>
+        <v>3.727370482232791</v>
       </c>
       <c r="E57">
-        <v>0.5780000000000001</v>
+        <v>0.6076000000000001</v>
       </c>
       <c r="F57">
-        <v>1.628</v>
+        <v>1.6576</v>
       </c>
       <c r="G57">
         <v>0.138</v>
@@ -5955,28 +5955,28 @@
         <v>1.168</v>
       </c>
       <c r="M57">
-        <v>0.0818884</v>
+        <v>0.08337728000000001</v>
       </c>
       <c r="N57">
-        <v>1.0861116</v>
+        <v>1.08462272</v>
       </c>
       <c r="O57">
-        <v>0.32583348</v>
+        <v>0.3253868159999999</v>
       </c>
       <c r="P57">
-        <v>0.7602781199999999</v>
+        <v>0.7592359039999999</v>
       </c>
       <c r="Q57">
-        <v>0.7522781199999999</v>
+        <v>0.7512359039999998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2661016694427347</v>
+        <v>0.2702990338578112</v>
       </c>
       <c r="T57">
-        <v>1.53604073492617</v>
+        <v>1.565306617192047</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>14.26331446212162</v>
+        <v>14.00861241815516</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1386491748974369</v>
+        <v>0.1381870985456433</v>
       </c>
       <c r="C58">
-        <v>2.207770482232791</v>
+        <v>2.196813017622757</v>
       </c>
       <c r="D58">
-        <v>3.727370482232791</v>
+        <v>3.746013017622757</v>
       </c>
       <c r="E58">
-        <v>0.6076000000000001</v>
+        <v>0.6372000000000002</v>
       </c>
       <c r="F58">
-        <v>1.6576</v>
+        <v>1.6872</v>
       </c>
       <c r="G58">
         <v>0.138</v>
@@ -6037,28 +6037,28 @@
         <v>1.168</v>
       </c>
       <c r="M58">
-        <v>0.08337728000000001</v>
+        <v>0.08486616000000001</v>
       </c>
       <c r="N58">
-        <v>1.08462272</v>
+        <v>1.08313384</v>
       </c>
       <c r="O58">
-        <v>0.3253868159999999</v>
+        <v>0.324940152</v>
       </c>
       <c r="P58">
-        <v>0.7592359039999999</v>
+        <v>0.758193688</v>
       </c>
       <c r="Q58">
-        <v>0.7512359039999998</v>
+        <v>0.750193688</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2702990338578112</v>
+        <v>0.2746916245247519</v>
       </c>
       <c r="T58">
-        <v>1.565306617192047</v>
+        <v>1.595933703284244</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>14.00861241815516</v>
+        <v>13.76284728801209</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1381870985456433</v>
+        <v>0.1377250221938496</v>
       </c>
       <c r="C59">
-        <v>2.196813017622757</v>
+        <v>2.186042972597415</v>
       </c>
       <c r="D59">
-        <v>3.746013017622757</v>
+        <v>3.764842972597415</v>
       </c>
       <c r="E59">
-        <v>0.6372000000000002</v>
+        <v>0.6668000000000001</v>
       </c>
       <c r="F59">
-        <v>1.6872</v>
+        <v>1.7168</v>
       </c>
       <c r="G59">
         <v>0.138</v>
@@ -6119,28 +6119,28 @@
         <v>1.168</v>
       </c>
       <c r="M59">
-        <v>0.08486616000000001</v>
+        <v>0.08635503999999999</v>
       </c>
       <c r="N59">
-        <v>1.08313384</v>
+        <v>1.08164496</v>
       </c>
       <c r="O59">
-        <v>0.324940152</v>
+        <v>0.324493488</v>
       </c>
       <c r="P59">
-        <v>0.758193688</v>
+        <v>0.757151472</v>
       </c>
       <c r="Q59">
-        <v>0.750193688</v>
+        <v>0.749151472</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2746916245247519</v>
+        <v>0.2792933861758325</v>
       </c>
       <c r="T59">
-        <v>1.595933703284244</v>
+        <v>1.628019222047497</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>13.76284728801209</v>
+        <v>13.52555681752912</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1377250221938497</v>
+        <v>0.137262945842056</v>
       </c>
       <c r="C60">
-        <v>2.186042972597414</v>
+        <v>2.175463187722104</v>
       </c>
       <c r="D60">
-        <v>3.764842972597414</v>
+        <v>3.783863187722104</v>
       </c>
       <c r="E60">
-        <v>0.6667999999999998</v>
+        <v>0.6963999999999999</v>
       </c>
       <c r="F60">
-        <v>1.7168</v>
+        <v>1.7464</v>
       </c>
       <c r="G60">
         <v>0.138</v>
@@ -6201,28 +6201,28 @@
         <v>1.168</v>
       </c>
       <c r="M60">
-        <v>0.08635503999999999</v>
+        <v>0.08784391999999999</v>
       </c>
       <c r="N60">
-        <v>1.08164496</v>
+        <v>1.08015608</v>
       </c>
       <c r="O60">
-        <v>0.324493488</v>
+        <v>0.324046824</v>
       </c>
       <c r="P60">
-        <v>0.757151472</v>
+        <v>0.7561092559999999</v>
       </c>
       <c r="Q60">
-        <v>0.749151472</v>
+        <v>0.7481092559999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2792933861758325</v>
+        <v>0.2841196240050146</v>
       </c>
       <c r="T60">
-        <v>1.628019222047497</v>
+        <v>1.661669888067495</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>13.52555681752912</v>
+        <v>13.29631009180829</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.137262945842056</v>
+        <v>0.1368008694902624</v>
       </c>
       <c r="C61">
-        <v>2.175463187722104</v>
+        <v>2.165076561256474</v>
       </c>
       <c r="D61">
-        <v>3.783863187722104</v>
+        <v>3.803076561256475</v>
       </c>
       <c r="E61">
-        <v>0.6963999999999999</v>
+        <v>0.726</v>
       </c>
       <c r="F61">
-        <v>1.7464</v>
+        <v>1.776</v>
       </c>
       <c r="G61">
         <v>0.138</v>
@@ -6283,28 +6283,28 @@
         <v>1.168</v>
       </c>
       <c r="M61">
-        <v>0.08784391999999999</v>
+        <v>0.08933279999999999</v>
       </c>
       <c r="N61">
-        <v>1.08015608</v>
+        <v>1.0786672</v>
       </c>
       <c r="O61">
-        <v>0.324046824</v>
+        <v>0.32360016</v>
       </c>
       <c r="P61">
-        <v>0.7561092559999999</v>
+        <v>0.7550670399999999</v>
       </c>
       <c r="Q61">
-        <v>0.7481092559999999</v>
+        <v>0.7470670399999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2841196240050146</v>
+        <v>0.2891871737256559</v>
       </c>
       <c r="T61">
-        <v>1.661669888067495</v>
+        <v>1.697003087388493</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>13.29631009180829</v>
+        <v>13.07470492361148</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1368008694902624</v>
+        <v>0.1369792931384687</v>
       </c>
       <c r="C62">
-        <v>2.165076561256474</v>
+        <v>2.128034533893564</v>
       </c>
       <c r="D62">
-        <v>3.803076561256475</v>
+        <v>3.795634533893563</v>
       </c>
       <c r="E62">
-        <v>0.726</v>
+        <v>0.7555999999999998</v>
       </c>
       <c r="F62">
-        <v>1.776</v>
+        <v>1.8056</v>
       </c>
       <c r="G62">
         <v>0.138</v>
@@ -6365,45 +6365,45 @@
         <v>1.168</v>
       </c>
       <c r="M62">
-        <v>0.08933279999999999</v>
+        <v>0.09353007999999999</v>
       </c>
       <c r="N62">
-        <v>1.0786672</v>
+        <v>1.07446992</v>
       </c>
       <c r="O62">
-        <v>0.32360016</v>
+        <v>0.3223409759999999</v>
       </c>
       <c r="P62">
-        <v>0.7550670399999999</v>
+        <v>0.7521289439999999</v>
       </c>
       <c r="Q62">
-        <v>0.7470670399999999</v>
+        <v>0.7441289439999998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2891871737256559</v>
+        <v>0.2945145977909454</v>
       </c>
       <c r="T62">
-        <v>1.697003087388493</v>
+        <v>1.734148245649029</v>
       </c>
       <c r="U62">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V62">
         <v>0.3</v>
       </c>
       <c r="W62">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y62">
-        <v>13.07470492361148</v>
+        <v>12.48796109230314</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1369792931384687</v>
+        <v>0.1365277167866751</v>
       </c>
       <c r="C63">
-        <v>2.128034533893564</v>
+        <v>2.117326432160856</v>
       </c>
       <c r="D63">
-        <v>3.795634533893563</v>
+        <v>3.814526432160856</v>
       </c>
       <c r="E63">
-        <v>0.7555999999999998</v>
+        <v>0.7851999999999999</v>
       </c>
       <c r="F63">
-        <v>1.8056</v>
+        <v>1.8352</v>
       </c>
       <c r="G63">
         <v>0.138</v>
@@ -6447,28 +6447,28 @@
         <v>1.168</v>
       </c>
       <c r="M63">
-        <v>0.09353007999999999</v>
+        <v>0.09506336</v>
       </c>
       <c r="N63">
-        <v>1.07446992</v>
+        <v>1.07293664</v>
       </c>
       <c r="O63">
-        <v>0.3223409759999999</v>
+        <v>0.321880992</v>
       </c>
       <c r="P63">
-        <v>0.7521289439999999</v>
+        <v>0.751055648</v>
       </c>
       <c r="Q63">
-        <v>0.7441289439999998</v>
+        <v>0.743055648</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2945145977909454</v>
+        <v>0.3001224125965134</v>
       </c>
       <c r="T63">
-        <v>1.734148245649029</v>
+        <v>1.773248412239067</v>
       </c>
       <c r="U63">
         <v>0.0518</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>12.48796109230314</v>
+        <v>12.28654236500793</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1365277167866751</v>
+        <v>0.1360761404348815</v>
       </c>
       <c r="C64">
-        <v>2.117326432160856</v>
+        <v>2.106807331297189</v>
       </c>
       <c r="D64">
-        <v>3.814526432160856</v>
+        <v>3.833607331297189</v>
       </c>
       <c r="E64">
-        <v>0.7851999999999999</v>
+        <v>0.8148</v>
       </c>
       <c r="F64">
-        <v>1.8352</v>
+        <v>1.8648</v>
       </c>
       <c r="G64">
         <v>0.138</v>
@@ -6529,28 +6529,28 @@
         <v>1.168</v>
       </c>
       <c r="M64">
-        <v>0.09506336</v>
+        <v>0.09659664</v>
       </c>
       <c r="N64">
-        <v>1.07293664</v>
+        <v>1.07140336</v>
       </c>
       <c r="O64">
-        <v>0.321880992</v>
+        <v>0.321421008</v>
       </c>
       <c r="P64">
-        <v>0.751055648</v>
+        <v>0.749982352</v>
       </c>
       <c r="Q64">
-        <v>0.743055648</v>
+        <v>0.741982352</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3001224125965134</v>
+        <v>0.3060333525267067</v>
       </c>
       <c r="T64">
-        <v>1.773248412239067</v>
+        <v>1.814462101347486</v>
       </c>
       <c r="U64">
         <v>0.0518</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>12.28654236500793</v>
+        <v>12.09151788302367</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1360761404348815</v>
+        <v>0.1356245640830878</v>
       </c>
       <c r="C65">
-        <v>2.106807331297189</v>
+        <v>2.096480081803112</v>
       </c>
       <c r="D65">
-        <v>3.833607331297189</v>
+        <v>3.852880081803112</v>
       </c>
       <c r="E65">
-        <v>0.8148</v>
+        <v>0.8444</v>
       </c>
       <c r="F65">
-        <v>1.8648</v>
+        <v>1.8944</v>
       </c>
       <c r="G65">
         <v>0.138</v>
@@ -6611,28 +6611,28 @@
         <v>1.168</v>
       </c>
       <c r="M65">
-        <v>0.09659664</v>
+        <v>0.09812992</v>
       </c>
       <c r="N65">
-        <v>1.07140336</v>
+        <v>1.06987008</v>
       </c>
       <c r="O65">
-        <v>0.321421008</v>
+        <v>0.3209610239999999</v>
       </c>
       <c r="P65">
-        <v>0.749982352</v>
+        <v>0.7489090559999999</v>
       </c>
       <c r="Q65">
-        <v>0.741982352</v>
+        <v>0.7409090559999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3060333525267067</v>
+        <v>0.3122726780085773</v>
       </c>
       <c r="T65">
-        <v>1.814462101347486</v>
+        <v>1.857965439850816</v>
       </c>
       <c r="U65">
         <v>0.0518</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>12.09151788302367</v>
+        <v>11.90258791610143</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1356245640830878</v>
+        <v>0.1351729877312942</v>
       </c>
       <c r="C66">
-        <v>2.096480081803112</v>
+        <v>2.086347591790247</v>
       </c>
       <c r="D66">
-        <v>3.852880081803112</v>
+        <v>3.872347591790247</v>
       </c>
       <c r="E66">
-        <v>0.8444</v>
+        <v>0.8739999999999999</v>
       </c>
       <c r="F66">
-        <v>1.8944</v>
+        <v>1.924</v>
       </c>
       <c r="G66">
         <v>0.138</v>
@@ -6693,28 +6693,28 @@
         <v>1.168</v>
       </c>
       <c r="M66">
-        <v>0.09812992</v>
+        <v>0.09966319999999999</v>
       </c>
       <c r="N66">
-        <v>1.06987008</v>
+        <v>1.0683368</v>
       </c>
       <c r="O66">
-        <v>0.3209610239999999</v>
+        <v>0.32050104</v>
       </c>
       <c r="P66">
-        <v>0.7489090559999999</v>
+        <v>0.7478357600000001</v>
       </c>
       <c r="Q66">
-        <v>0.7409090559999999</v>
+        <v>0.7398357600000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3122726780085773</v>
+        <v>0.3188685363751262</v>
       </c>
       <c r="T66">
-        <v>1.857965439850816</v>
+        <v>1.90395468341148</v>
       </c>
       <c r="U66">
         <v>0.0518</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>11.90258791610143</v>
+        <v>11.71947117893064</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1351729877312942</v>
+        <v>0.1347214113795005</v>
       </c>
       <c r="C67">
-        <v>2.086347591790247</v>
+        <v>2.076412828444158</v>
       </c>
       <c r="D67">
-        <v>3.872347591790247</v>
+        <v>3.892012828444158</v>
       </c>
       <c r="E67">
-        <v>0.8739999999999999</v>
+        <v>0.9036</v>
       </c>
       <c r="F67">
-        <v>1.924</v>
+        <v>1.9536</v>
       </c>
       <c r="G67">
         <v>0.138</v>
@@ -6775,28 +6775,28 @@
         <v>1.168</v>
       </c>
       <c r="M67">
-        <v>0.09966319999999999</v>
+        <v>0.10119648</v>
       </c>
       <c r="N67">
-        <v>1.0683368</v>
+        <v>1.06680352</v>
       </c>
       <c r="O67">
-        <v>0.32050104</v>
+        <v>0.3200410559999999</v>
       </c>
       <c r="P67">
-        <v>0.7478357600000001</v>
+        <v>0.7467624639999999</v>
       </c>
       <c r="Q67">
-        <v>0.7398357600000001</v>
+        <v>0.7387624639999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3188685363751262</v>
+        <v>0.3258523864102957</v>
       </c>
       <c r="T67">
-        <v>1.90395468341148</v>
+        <v>1.952649176593359</v>
       </c>
       <c r="U67">
         <v>0.0518</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>11.71947117893064</v>
+        <v>11.54190343379533</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1347214113795005</v>
+        <v>0.1342698350277069</v>
       </c>
       <c r="C68">
-        <v>2.076412828444158</v>
+        <v>2.066678819531995</v>
       </c>
       <c r="D68">
-        <v>3.892012828444158</v>
+        <v>3.911878819531995</v>
       </c>
       <c r="E68">
-        <v>0.9036</v>
+        <v>0.9332</v>
       </c>
       <c r="F68">
-        <v>1.9536</v>
+        <v>1.9832</v>
       </c>
       <c r="G68">
         <v>0.138</v>
@@ -6857,28 +6857,28 @@
         <v>1.168</v>
       </c>
       <c r="M68">
-        <v>0.10119648</v>
+        <v>0.10272976</v>
       </c>
       <c r="N68">
-        <v>1.06680352</v>
+        <v>1.06527024</v>
       </c>
       <c r="O68">
-        <v>0.3200410559999999</v>
+        <v>0.3195810719999999</v>
       </c>
       <c r="P68">
-        <v>0.7467624639999999</v>
+        <v>0.745689168</v>
       </c>
       <c r="Q68">
-        <v>0.7387624639999999</v>
+        <v>0.737689168</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3258523864102957</v>
+        <v>0.3332595000839603</v>
       </c>
       <c r="T68">
-        <v>1.952649176593359</v>
+        <v>2.004294851180201</v>
       </c>
       <c r="U68">
         <v>0.0518</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>11.54190343379533</v>
+        <v>11.36963621836554</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1342698350277069</v>
+        <v>0.1338182586759132</v>
       </c>
       <c r="C69">
-        <v>2.066678819531995</v>
+        <v>2.057148654956567</v>
       </c>
       <c r="D69">
-        <v>3.911878819531995</v>
+        <v>3.931948654956567</v>
       </c>
       <c r="E69">
-        <v>0.9332</v>
+        <v>0.9627999999999999</v>
       </c>
       <c r="F69">
-        <v>1.9832</v>
+        <v>2.0128</v>
       </c>
       <c r="G69">
         <v>0.138</v>
@@ -6939,28 +6939,28 @@
         <v>1.168</v>
       </c>
       <c r="M69">
-        <v>0.10272976</v>
+        <v>0.10426304</v>
       </c>
       <c r="N69">
-        <v>1.06527024</v>
+        <v>1.06373696</v>
       </c>
       <c r="O69">
-        <v>0.3195810719999999</v>
+        <v>0.319121088</v>
       </c>
       <c r="P69">
-        <v>0.745689168</v>
+        <v>0.744615872</v>
       </c>
       <c r="Q69">
-        <v>0.737689168</v>
+        <v>0.736615872</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3332595000839603</v>
+        <v>0.3411295583622289</v>
       </c>
       <c r="T69">
-        <v>2.004294851180201</v>
+        <v>2.05916838042872</v>
       </c>
       <c r="U69">
         <v>0.0518</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>11.36963621836554</v>
+        <v>11.20243568574252</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1338182586759132</v>
+        <v>0.1333666823241196</v>
       </c>
       <c r="C70">
-        <v>2.057148654956567</v>
+        <v>2.047825488358489</v>
       </c>
       <c r="D70">
-        <v>3.931948654956567</v>
+        <v>3.952225488358489</v>
       </c>
       <c r="E70">
-        <v>0.9627999999999999</v>
+        <v>0.9924000000000002</v>
       </c>
       <c r="F70">
-        <v>2.0128</v>
+        <v>2.0424</v>
       </c>
       <c r="G70">
         <v>0.138</v>
@@ -7021,28 +7021,28 @@
         <v>1.168</v>
       </c>
       <c r="M70">
-        <v>0.10426304</v>
+        <v>0.10579632</v>
       </c>
       <c r="N70">
-        <v>1.06373696</v>
+        <v>1.06220368</v>
       </c>
       <c r="O70">
-        <v>0.319121088</v>
+        <v>0.318661104</v>
       </c>
       <c r="P70">
-        <v>0.744615872</v>
+        <v>0.7435425759999998</v>
       </c>
       <c r="Q70">
-        <v>0.736615872</v>
+        <v>0.7355425759999998</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3411295583622289</v>
+        <v>0.3495073623358698</v>
       </c>
       <c r="T70">
-        <v>2.05916838042872</v>
+        <v>2.117582137370693</v>
       </c>
       <c r="U70">
         <v>0.0518</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>11.20243568574252</v>
+        <v>11.04008154536944</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1333666823241196</v>
+        <v>0.1329151059723259</v>
       </c>
       <c r="C71">
-        <v>2.047825488358489</v>
+        <v>2.03871253876816</v>
       </c>
       <c r="D71">
-        <v>3.952225488358489</v>
+        <v>3.97271253876816</v>
       </c>
       <c r="E71">
-        <v>0.9924000000000002</v>
+        <v>1.022</v>
       </c>
       <c r="F71">
-        <v>2.0424</v>
+        <v>2.072</v>
       </c>
       <c r="G71">
         <v>0.138</v>
@@ -7103,28 +7103,28 @@
         <v>1.168</v>
       </c>
       <c r="M71">
-        <v>0.10579632</v>
+        <v>0.1073296</v>
       </c>
       <c r="N71">
-        <v>1.06220368</v>
+        <v>1.0606704</v>
       </c>
       <c r="O71">
-        <v>0.318661104</v>
+        <v>0.31820112</v>
       </c>
       <c r="P71">
-        <v>0.7435425759999998</v>
+        <v>0.74246928</v>
       </c>
       <c r="Q71">
-        <v>0.7355425759999998</v>
+        <v>0.73446928</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3495073623358698</v>
+        <v>0.3584436865744199</v>
       </c>
       <c r="T71">
-        <v>2.117582137370693</v>
+        <v>2.179890144775463</v>
       </c>
       <c r="U71">
         <v>0.0518</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>11.04008154536944</v>
+        <v>10.88236609472131</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1329151059723259</v>
+        <v>0.1324635296205323</v>
       </c>
       <c r="C72">
-        <v>2.03871253876816</v>
+        <v>2.02981309230939</v>
       </c>
       <c r="D72">
-        <v>3.97271253876816</v>
+        <v>3.99341309230939</v>
       </c>
       <c r="E72">
-        <v>1.022</v>
+        <v>1.0516</v>
       </c>
       <c r="F72">
-        <v>2.072</v>
+        <v>2.1016</v>
       </c>
       <c r="G72">
         <v>0.138</v>
@@ -7185,28 +7185,28 @@
         <v>1.168</v>
       </c>
       <c r="M72">
-        <v>0.1073296</v>
+        <v>0.10886288</v>
       </c>
       <c r="N72">
-        <v>1.0606704</v>
+        <v>1.05913712</v>
       </c>
       <c r="O72">
-        <v>0.31820112</v>
+        <v>0.317741136</v>
       </c>
       <c r="P72">
-        <v>0.74246928</v>
+        <v>0.741395984</v>
       </c>
       <c r="Q72">
-        <v>0.73446928</v>
+        <v>0.7333959839999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3584436865744199</v>
+        <v>0.3679963090363184</v>
       </c>
       <c r="T72">
-        <v>2.179890144775463</v>
+        <v>2.246495256139183</v>
       </c>
       <c r="U72">
         <v>0.0518</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>10.88236609472131</v>
+        <v>10.72909333282382</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1324635296205323</v>
+        <v>0.1320119532687387</v>
       </c>
       <c r="C73">
-        <v>2.029813092309389</v>
+        <v>2.021130503956575</v>
       </c>
       <c r="D73">
-        <v>3.993413092309389</v>
+        <v>4.014330503956574</v>
       </c>
       <c r="E73">
-        <v>1.0516</v>
+        <v>1.0812</v>
       </c>
       <c r="F73">
-        <v>2.1016</v>
+        <v>2.1312</v>
       </c>
       <c r="G73">
         <v>0.138</v>
@@ -7267,28 +7267,28 @@
         <v>1.168</v>
       </c>
       <c r="M73">
-        <v>0.10886288</v>
+        <v>0.11039616</v>
       </c>
       <c r="N73">
-        <v>1.05913712</v>
+        <v>1.05760384</v>
       </c>
       <c r="O73">
-        <v>0.317741136</v>
+        <v>0.317281152</v>
       </c>
       <c r="P73">
-        <v>0.741395984</v>
+        <v>0.7403226879999999</v>
       </c>
       <c r="Q73">
-        <v>0.7333959839999999</v>
+        <v>0.7323226879999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3679963090363183</v>
+        <v>0.3782312616740667</v>
       </c>
       <c r="T73">
-        <v>2.246495256139182</v>
+        <v>2.317857875457454</v>
       </c>
       <c r="U73">
         <v>0.0518</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>10.72909333282382</v>
+        <v>10.58007814764572</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1320119532687387</v>
+        <v>0.131560376916945</v>
       </c>
       <c r="C74">
-        <v>2.021130503956575</v>
+        <v>2.012668199347374</v>
       </c>
       <c r="D74">
-        <v>4.014330503956574</v>
+        <v>4.035468199347374</v>
       </c>
       <c r="E74">
-        <v>1.0812</v>
+        <v>1.1108</v>
       </c>
       <c r="F74">
-        <v>2.1312</v>
+        <v>2.1608</v>
       </c>
       <c r="G74">
         <v>0.138</v>
@@ -7349,28 +7349,28 @@
         <v>1.168</v>
       </c>
       <c r="M74">
-        <v>0.11039616</v>
+        <v>0.11192944</v>
       </c>
       <c r="N74">
-        <v>1.05760384</v>
+        <v>1.05607056</v>
       </c>
       <c r="O74">
-        <v>0.317281152</v>
+        <v>0.316821168</v>
       </c>
       <c r="P74">
-        <v>0.7403226879999999</v>
+        <v>0.7392493920000001</v>
       </c>
       <c r="Q74">
-        <v>0.7323226879999999</v>
+        <v>0.7312493920000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3782312616740667</v>
+        <v>0.3892243589516483</v>
       </c>
       <c r="T74">
-        <v>2.317857875457454</v>
+        <v>2.394506614725227</v>
       </c>
       <c r="U74">
         <v>0.0518</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>10.58007814764572</v>
+        <v>10.4351455702807</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.131560376916945</v>
+        <v>0.1311088005651514</v>
       </c>
       <c r="C75">
-        <v>2.012668199347374</v>
+        <v>2.004429676652976</v>
       </c>
       <c r="D75">
-        <v>4.035468199347374</v>
+        <v>4.056829676652976</v>
       </c>
       <c r="E75">
-        <v>1.1108</v>
+        <v>1.1404</v>
       </c>
       <c r="F75">
-        <v>2.1608</v>
+        <v>2.1904</v>
       </c>
       <c r="G75">
         <v>0.138</v>
@@ -7431,28 +7431,28 @@
         <v>1.168</v>
       </c>
       <c r="M75">
-        <v>0.11192944</v>
+        <v>0.11346272</v>
       </c>
       <c r="N75">
-        <v>1.05607056</v>
+        <v>1.05453728</v>
       </c>
       <c r="O75">
-        <v>0.316821168</v>
+        <v>0.316361184</v>
       </c>
       <c r="P75">
-        <v>0.7392493920000001</v>
+        <v>0.7381760959999999</v>
       </c>
       <c r="Q75">
-        <v>0.7312493920000001</v>
+        <v>0.7301760959999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3892243589516483</v>
+        <v>0.4010630790967361</v>
       </c>
       <c r="T75">
-        <v>2.394506614725227</v>
+        <v>2.477051410859751</v>
       </c>
       <c r="U75">
         <v>0.0518</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>10.4351455702807</v>
+        <v>10.29413008960124</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1311088005651514</v>
+        <v>0.1306572242133577</v>
       </c>
       <c r="C76">
-        <v>2.004429676652976</v>
+        <v>1.996418508508058</v>
       </c>
       <c r="D76">
-        <v>4.056829676652976</v>
+        <v>4.078418508508058</v>
       </c>
       <c r="E76">
-        <v>1.1404</v>
+        <v>1.17</v>
       </c>
       <c r="F76">
-        <v>2.1904</v>
+        <v>2.22</v>
       </c>
       <c r="G76">
         <v>0.138</v>
@@ -7513,28 +7513,28 @@
         <v>1.168</v>
       </c>
       <c r="M76">
-        <v>0.11346272</v>
+        <v>0.114996</v>
       </c>
       <c r="N76">
-        <v>1.05453728</v>
+        <v>1.053004</v>
       </c>
       <c r="O76">
-        <v>0.316361184</v>
+        <v>0.3159012</v>
       </c>
       <c r="P76">
-        <v>0.7381760959999999</v>
+        <v>0.7371028000000001</v>
       </c>
       <c r="Q76">
-        <v>0.7301760959999999</v>
+        <v>0.7291028000000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4010630790967361</v>
+        <v>0.4138488968534309</v>
       </c>
       <c r="T76">
-        <v>2.477051410859751</v>
+        <v>2.566199790685038</v>
       </c>
       <c r="U76">
         <v>0.0518</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>10.29413008960124</v>
+        <v>10.15687502173989</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1306572242133577</v>
+        <v>0.1302056478615641</v>
       </c>
       <c r="C77">
-        <v>1.996418508508058</v>
+        <v>1.98863834400272</v>
       </c>
       <c r="D77">
-        <v>4.078418508508058</v>
+        <v>4.100238344002721</v>
       </c>
       <c r="E77">
-        <v>1.17</v>
+        <v>1.1996</v>
       </c>
       <c r="F77">
-        <v>2.22</v>
+        <v>2.2496</v>
       </c>
       <c r="G77">
         <v>0.138</v>
@@ -7595,28 +7595,28 @@
         <v>1.168</v>
       </c>
       <c r="M77">
-        <v>0.114996</v>
+        <v>0.11652928</v>
       </c>
       <c r="N77">
-        <v>1.053004</v>
+        <v>1.05147072</v>
       </c>
       <c r="O77">
-        <v>0.3159012</v>
+        <v>0.315441216</v>
       </c>
       <c r="P77">
-        <v>0.7371028000000001</v>
+        <v>0.736029504</v>
       </c>
       <c r="Q77">
-        <v>0.7291028000000001</v>
+        <v>0.728029504</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4138488968534309</v>
+        <v>0.4277001994231837</v>
       </c>
       <c r="T77">
-        <v>2.566199790685038</v>
+        <v>2.662777202162432</v>
       </c>
       <c r="U77">
         <v>0.0518</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>10.15687502173989</v>
+        <v>10.02323192934857</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1302056478615641</v>
+        <v>0.1297540715097704</v>
       </c>
       <c r="C78">
-        <v>1.98863834400272</v>
+        <v>1.981092910738696</v>
       </c>
       <c r="D78">
-        <v>4.100238344002721</v>
+        <v>4.122292910738696</v>
       </c>
       <c r="E78">
-        <v>1.1996</v>
+        <v>1.2292</v>
       </c>
       <c r="F78">
-        <v>2.2496</v>
+        <v>2.2792</v>
       </c>
       <c r="G78">
         <v>0.138</v>
@@ -7677,28 +7677,28 @@
         <v>1.168</v>
       </c>
       <c r="M78">
-        <v>0.11652928</v>
+        <v>0.11806256</v>
       </c>
       <c r="N78">
-        <v>1.05147072</v>
+        <v>1.04993744</v>
       </c>
       <c r="O78">
-        <v>0.315441216</v>
+        <v>0.3149812319999999</v>
       </c>
       <c r="P78">
-        <v>0.736029504</v>
+        <v>0.7349562079999999</v>
       </c>
       <c r="Q78">
-        <v>0.728029504</v>
+        <v>0.7269562079999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4277001994231837</v>
+        <v>0.4427559630859585</v>
       </c>
       <c r="T78">
-        <v>2.662777202162432</v>
+        <v>2.767752649420469</v>
       </c>
       <c r="U78">
         <v>0.0518</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>10.02323192934857</v>
+        <v>9.893060086110278</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1297540715097704</v>
+        <v>0.1302306951579768</v>
       </c>
       <c r="C79">
-        <v>1.981092910738696</v>
+        <v>1.928221963100337</v>
       </c>
       <c r="D79">
-        <v>4.122292910738696</v>
+        <v>4.099021963100338</v>
       </c>
       <c r="E79">
-        <v>1.2292</v>
+        <v>1.2588</v>
       </c>
       <c r="F79">
-        <v>2.2792</v>
+        <v>2.3088</v>
       </c>
       <c r="G79">
         <v>0.138</v>
@@ -7759,45 +7759,45 @@
         <v>1.168</v>
       </c>
       <c r="M79">
-        <v>0.11806256</v>
+        <v>0.1235208</v>
       </c>
       <c r="N79">
-        <v>1.04993744</v>
+        <v>1.0444792</v>
       </c>
       <c r="O79">
-        <v>0.3149812319999999</v>
+        <v>0.3133437599999999</v>
       </c>
       <c r="P79">
-        <v>0.7349562079999999</v>
+        <v>0.7311354399999999</v>
       </c>
       <c r="Q79">
-        <v>0.7269562079999999</v>
+        <v>0.7231354399999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4427559630859585</v>
+        <v>0.4591804325362582</v>
       </c>
       <c r="T79">
-        <v>2.767752649420469</v>
+        <v>2.882271319156509</v>
       </c>
       <c r="U79">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V79">
         <v>0.3</v>
       </c>
       <c r="W79">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>9.893060086110278</v>
+        <v>9.455897306364594</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1302306951579768</v>
+        <v>0.1297910188061832</v>
       </c>
       <c r="C80">
-        <v>1.928221963100337</v>
+        <v>1.920079531400787</v>
       </c>
       <c r="D80">
-        <v>4.099021963100338</v>
+        <v>4.120479531400787</v>
       </c>
       <c r="E80">
-        <v>1.2588</v>
+        <v>1.2884</v>
       </c>
       <c r="F80">
-        <v>2.3088</v>
+        <v>2.3384</v>
       </c>
       <c r="G80">
         <v>0.138</v>
@@ -7841,28 +7841,28 @@
         <v>1.168</v>
       </c>
       <c r="M80">
-        <v>0.1235208</v>
+        <v>0.1251044</v>
       </c>
       <c r="N80">
-        <v>1.0444792</v>
+        <v>1.0428956</v>
       </c>
       <c r="O80">
-        <v>0.3133437599999999</v>
+        <v>0.31286868</v>
       </c>
       <c r="P80">
-        <v>0.7311354399999999</v>
+        <v>0.73002692</v>
       </c>
       <c r="Q80">
-        <v>0.7231354399999999</v>
+        <v>0.72202692</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4591804325362582</v>
+        <v>0.4771691371723009</v>
       </c>
       <c r="T80">
-        <v>2.882271319156509</v>
+        <v>3.00769652886741</v>
       </c>
       <c r="U80">
         <v>0.0535</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>9.455897306364594</v>
+        <v>9.336202403752386</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1297910188061832</v>
+        <v>0.1293513424543895</v>
       </c>
       <c r="C81">
-        <v>1.920079531400787</v>
+        <v>1.912162934141989</v>
       </c>
       <c r="D81">
-        <v>4.120479531400787</v>
+        <v>4.142162934141989</v>
       </c>
       <c r="E81">
-        <v>1.2884</v>
+        <v>1.318</v>
       </c>
       <c r="F81">
-        <v>2.3384</v>
+        <v>2.368</v>
       </c>
       <c r="G81">
         <v>0.138</v>
@@ -7923,28 +7923,28 @@
         <v>1.168</v>
       </c>
       <c r="M81">
-        <v>0.1251044</v>
+        <v>0.126688</v>
       </c>
       <c r="N81">
-        <v>1.0428956</v>
+        <v>1.041312</v>
       </c>
       <c r="O81">
-        <v>0.31286868</v>
+        <v>0.3123936</v>
       </c>
       <c r="P81">
-        <v>0.73002692</v>
+        <v>0.7289184</v>
       </c>
       <c r="Q81">
-        <v>0.72202692</v>
+        <v>0.7209184</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4771691371723009</v>
+        <v>0.4969567122719477</v>
       </c>
       <c r="T81">
-        <v>3.00769652886741</v>
+        <v>3.145664259549402</v>
       </c>
       <c r="U81">
         <v>0.0535</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>9.336202403752386</v>
+        <v>9.219499873705482</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1293513424543895</v>
+        <v>0.1289116661025959</v>
       </c>
       <c r="C82">
-        <v>1.912162934141989</v>
+        <v>1.904475755443998</v>
       </c>
       <c r="D82">
-        <v>4.142162934141989</v>
+        <v>4.164075755443998</v>
       </c>
       <c r="E82">
-        <v>1.318</v>
+        <v>1.3476</v>
       </c>
       <c r="F82">
-        <v>2.368</v>
+        <v>2.3976</v>
       </c>
       <c r="G82">
         <v>0.138</v>
@@ -8005,28 +8005,28 @@
         <v>1.168</v>
       </c>
       <c r="M82">
-        <v>0.126688</v>
+        <v>0.1282716</v>
       </c>
       <c r="N82">
-        <v>1.041312</v>
+        <v>1.0397284</v>
       </c>
       <c r="O82">
-        <v>0.3123936</v>
+        <v>0.31191852</v>
       </c>
       <c r="P82">
-        <v>0.7289184</v>
+        <v>0.72780988</v>
       </c>
       <c r="Q82">
-        <v>0.7209184</v>
+        <v>0.71980988</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4969567122719477</v>
+        <v>0.5188271900136626</v>
       </c>
       <c r="T82">
-        <v>3.145664259549402</v>
+        <v>3.29815490925055</v>
       </c>
       <c r="U82">
         <v>0.0535</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>9.219499873705482</v>
+        <v>9.105678887610351</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1289116661025959</v>
+        <v>0.1284719897508022</v>
       </c>
       <c r="C83">
-        <v>1.904475755443998</v>
+        <v>1.897021655672899</v>
       </c>
       <c r="D83">
-        <v>4.164075755443998</v>
+        <v>4.186221655672899</v>
       </c>
       <c r="E83">
-        <v>1.3476</v>
+        <v>1.3772</v>
       </c>
       <c r="F83">
-        <v>2.3976</v>
+        <v>2.4272</v>
       </c>
       <c r="G83">
         <v>0.138</v>
@@ -8087,28 +8087,28 @@
         <v>1.168</v>
       </c>
       <c r="M83">
-        <v>0.1282716</v>
+        <v>0.1298552</v>
       </c>
       <c r="N83">
-        <v>1.0397284</v>
+        <v>1.0381448</v>
       </c>
       <c r="O83">
-        <v>0.31191852</v>
+        <v>0.31144344</v>
       </c>
       <c r="P83">
-        <v>0.72780988</v>
+        <v>0.7267013600000001</v>
       </c>
       <c r="Q83">
-        <v>0.71980988</v>
+        <v>0.7187013600000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5188271900136626</v>
+        <v>0.5431277208377904</v>
       </c>
       <c r="T83">
-        <v>3.29815490925055</v>
+        <v>3.467588964474049</v>
       </c>
       <c r="U83">
         <v>0.0535</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>9.105678887610351</v>
+        <v>8.994634023127297</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1284719897508022</v>
+        <v>0.1280323133990086</v>
       </c>
       <c r="C84">
-        <v>1.897021655672899</v>
+        <v>1.889804373479158</v>
       </c>
       <c r="D84">
-        <v>4.186221655672899</v>
+        <v>4.208604373479158</v>
       </c>
       <c r="E84">
-        <v>1.3772</v>
+        <v>1.4068</v>
       </c>
       <c r="F84">
-        <v>2.4272</v>
+        <v>2.4568</v>
       </c>
       <c r="G84">
         <v>0.138</v>
@@ -8169,28 +8169,28 @@
         <v>1.168</v>
       </c>
       <c r="M84">
-        <v>0.1298552</v>
+        <v>0.1314388</v>
       </c>
       <c r="N84">
-        <v>1.0381448</v>
+        <v>1.0365612</v>
       </c>
       <c r="O84">
-        <v>0.31144344</v>
+        <v>0.31096836</v>
       </c>
       <c r="P84">
-        <v>0.7267013600000001</v>
+        <v>0.72559284</v>
       </c>
       <c r="Q84">
-        <v>0.7187013600000001</v>
+        <v>0.71759284</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5431277208377904</v>
+        <v>0.5702871376412272</v>
       </c>
       <c r="T84">
-        <v>3.467588964474049</v>
+        <v>3.656956437959135</v>
       </c>
       <c r="U84">
         <v>0.0535</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>8.994634023127297</v>
+        <v>8.886264938511307</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1280323133990086</v>
+        <v>0.127592637047215</v>
       </c>
       <c r="C85">
-        <v>1.889804373479158</v>
+        <v>1.882827727901705</v>
       </c>
       <c r="D85">
-        <v>4.208604373479158</v>
+        <v>4.231227727901706</v>
       </c>
       <c r="E85">
-        <v>1.4068</v>
+        <v>1.4364</v>
       </c>
       <c r="F85">
-        <v>2.4568</v>
+        <v>2.4864</v>
       </c>
       <c r="G85">
         <v>0.138</v>
@@ -8251,28 +8251,28 @@
         <v>1.168</v>
       </c>
       <c r="M85">
-        <v>0.1314388</v>
+        <v>0.1330224</v>
       </c>
       <c r="N85">
-        <v>1.0365612</v>
+        <v>1.0349776</v>
       </c>
       <c r="O85">
-        <v>0.31096836</v>
+        <v>0.31049328</v>
       </c>
       <c r="P85">
-        <v>0.72559284</v>
+        <v>0.72448432</v>
       </c>
       <c r="Q85">
-        <v>0.71759284</v>
+        <v>0.71648432</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5702871376412272</v>
+        <v>0.6008414815450938</v>
       </c>
       <c r="T85">
-        <v>3.656956437959135</v>
+        <v>3.869994845629858</v>
       </c>
       <c r="U85">
         <v>0.0535</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>8.886264938511307</v>
+        <v>8.780476070195695</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.127592637047215</v>
+        <v>0.1271529606954213</v>
       </c>
       <c r="C86">
-        <v>1.882827727901706</v>
+        <v>1.876095620540267</v>
       </c>
       <c r="D86">
-        <v>4.231227727901706</v>
+        <v>4.254095620540267</v>
       </c>
       <c r="E86">
-        <v>1.4364</v>
+        <v>1.466</v>
       </c>
       <c r="F86">
-        <v>2.4864</v>
+        <v>2.516</v>
       </c>
       <c r="G86">
         <v>0.138</v>
@@ -8333,28 +8333,28 @@
         <v>1.168</v>
       </c>
       <c r="M86">
-        <v>0.1330224</v>
+        <v>0.134606</v>
       </c>
       <c r="N86">
-        <v>1.0349776</v>
+        <v>1.033394</v>
       </c>
       <c r="O86">
-        <v>0.31049328</v>
+        <v>0.3100182</v>
       </c>
       <c r="P86">
-        <v>0.72448432</v>
+        <v>0.7233757999999999</v>
       </c>
       <c r="Q86">
-        <v>0.71648432</v>
+        <v>0.7153757999999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6008414815450933</v>
+        <v>0.6354697379694753</v>
       </c>
       <c r="T86">
-        <v>3.869994845629855</v>
+        <v>4.11143837432334</v>
       </c>
       <c r="U86">
         <v>0.0535</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>8.780476070195697</v>
+        <v>8.677176351722805</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1271529606954213</v>
+        <v>0.1267132843436277</v>
       </c>
       <c r="C87">
-        <v>1.876095620540267</v>
+        <v>1.869612037798489</v>
       </c>
       <c r="D87">
-        <v>4.254095620540267</v>
+        <v>4.277212037798489</v>
       </c>
       <c r="E87">
-        <v>1.466</v>
+        <v>1.4956</v>
       </c>
       <c r="F87">
-        <v>2.516</v>
+        <v>2.5456</v>
       </c>
       <c r="G87">
         <v>0.138</v>
@@ -8415,28 +8415,28 @@
         <v>1.168</v>
       </c>
       <c r="M87">
-        <v>0.134606</v>
+        <v>0.1361896</v>
       </c>
       <c r="N87">
-        <v>1.033394</v>
+        <v>1.0318104</v>
       </c>
       <c r="O87">
-        <v>0.3100182</v>
+        <v>0.3095431199999999</v>
       </c>
       <c r="P87">
-        <v>0.7233757999999999</v>
+        <v>0.72226728</v>
       </c>
       <c r="Q87">
-        <v>0.7153757999999999</v>
+        <v>0.7142672799999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6354697379694753</v>
+        <v>0.6750448881687688</v>
       </c>
       <c r="T87">
-        <v>4.11143837432334</v>
+        <v>4.387373835687322</v>
       </c>
       <c r="U87">
         <v>0.0535</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>8.677176351722805</v>
+        <v>8.576278952284168</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1267132843436277</v>
+        <v>0.126273607991834</v>
       </c>
       <c r="C88">
-        <v>1.869612037798489</v>
+        <v>1.863381053200631</v>
       </c>
       <c r="D88">
-        <v>4.277212037798489</v>
+        <v>4.300581053200631</v>
       </c>
       <c r="E88">
-        <v>1.4956</v>
+        <v>1.5252</v>
       </c>
       <c r="F88">
-        <v>2.5456</v>
+        <v>2.5752</v>
       </c>
       <c r="G88">
         <v>0.138</v>
@@ -8497,28 +8497,28 @@
         <v>1.168</v>
       </c>
       <c r="M88">
-        <v>0.1361896</v>
+        <v>0.1377732</v>
       </c>
       <c r="N88">
-        <v>1.0318104</v>
+        <v>1.0302268</v>
       </c>
       <c r="O88">
-        <v>0.3095431199999999</v>
+        <v>0.3090680399999999</v>
       </c>
       <c r="P88">
-        <v>0.72226728</v>
+        <v>0.72115876</v>
       </c>
       <c r="Q88">
-        <v>0.7142672799999999</v>
+        <v>0.71315876</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6750448881687688</v>
+        <v>0.7207085230141077</v>
       </c>
       <c r="T88">
-        <v>4.387373835687322</v>
+        <v>4.705760906491918</v>
       </c>
       <c r="U88">
         <v>0.0535</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>8.576278952284168</v>
+        <v>8.477701033292394</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.126273607991834</v>
+        <v>0.1258339316400404</v>
       </c>
       <c r="C89">
-        <v>1.863381053200631</v>
+        <v>1.857406829784599</v>
       </c>
       <c r="D89">
-        <v>4.300581053200631</v>
+        <v>4.324206829784599</v>
       </c>
       <c r="E89">
-        <v>1.5252</v>
+        <v>1.5548</v>
       </c>
       <c r="F89">
-        <v>2.5752</v>
+        <v>2.6048</v>
       </c>
       <c r="G89">
         <v>0.138</v>
@@ -8579,28 +8579,28 @@
         <v>1.168</v>
       </c>
       <c r="M89">
-        <v>0.1377732</v>
+        <v>0.1393568</v>
       </c>
       <c r="N89">
-        <v>1.0302268</v>
+        <v>1.0286432</v>
       </c>
       <c r="O89">
-        <v>0.3090680399999999</v>
+        <v>0.30859296</v>
       </c>
       <c r="P89">
-        <v>0.72115876</v>
+        <v>0.72005024</v>
       </c>
       <c r="Q89">
-        <v>0.71315876</v>
+        <v>0.7120502399999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7207085230141077</v>
+        <v>0.7739827636670031</v>
       </c>
       <c r="T89">
-        <v>4.705760906491918</v>
+        <v>5.077212489097279</v>
       </c>
       <c r="U89">
         <v>0.0535</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>8.477701033292394</v>
+        <v>8.381363521550437</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1258339316400404</v>
+        <v>0.1253942552882467</v>
       </c>
       <c r="C90">
-        <v>1.857406829784599</v>
+        <v>1.851693622574299</v>
       </c>
       <c r="D90">
-        <v>4.324206829784599</v>
+        <v>4.348093622574299</v>
       </c>
       <c r="E90">
-        <v>1.5548</v>
+        <v>1.5844</v>
       </c>
       <c r="F90">
-        <v>2.6048</v>
+        <v>2.6344</v>
       </c>
       <c r="G90">
         <v>0.138</v>
@@ -8661,28 +8661,28 @@
         <v>1.168</v>
       </c>
       <c r="M90">
-        <v>0.1393568</v>
+        <v>0.1409404</v>
       </c>
       <c r="N90">
-        <v>1.0286432</v>
+        <v>1.0270596</v>
       </c>
       <c r="O90">
-        <v>0.30859296</v>
+        <v>0.30811788</v>
       </c>
       <c r="P90">
-        <v>0.72005024</v>
+        <v>0.7189417199999999</v>
       </c>
       <c r="Q90">
-        <v>0.7120502399999999</v>
+        <v>0.7109417199999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7739827636670031</v>
+        <v>0.8369432298931522</v>
       </c>
       <c r="T90">
-        <v>5.077212489097279</v>
+        <v>5.516200723085434</v>
       </c>
       <c r="U90">
         <v>0.0535</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>8.381363521550437</v>
+        <v>8.28719089771279</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1253942552882467</v>
+        <v>0.1249545789364531</v>
       </c>
       <c r="C91">
-        <v>1.851693622574299</v>
+        <v>1.846245781134394</v>
       </c>
       <c r="D91">
-        <v>4.348093622574299</v>
+        <v>4.372245781134394</v>
       </c>
       <c r="E91">
-        <v>1.5844</v>
+        <v>1.614</v>
       </c>
       <c r="F91">
-        <v>2.6344</v>
+        <v>2.664</v>
       </c>
       <c r="G91">
         <v>0.138</v>
@@ -8743,28 +8743,28 @@
         <v>1.168</v>
       </c>
       <c r="M91">
-        <v>0.1409404</v>
+        <v>0.142524</v>
       </c>
       <c r="N91">
-        <v>1.0270596</v>
+        <v>1.025476</v>
       </c>
       <c r="O91">
-        <v>0.30811788</v>
+        <v>0.3076427999999999</v>
       </c>
       <c r="P91">
-        <v>0.7189417199999999</v>
+        <v>0.7178331999999998</v>
       </c>
       <c r="Q91">
-        <v>0.7109417199999999</v>
+        <v>0.7098331999999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8369432298931522</v>
+        <v>0.9124957893645309</v>
       </c>
       <c r="T91">
-        <v>5.516200723085434</v>
+        <v>6.042986603871219</v>
       </c>
       <c r="U91">
         <v>0.0535</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>8.28719089771279</v>
+        <v>8.195110998849316</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1249545789364531</v>
+        <v>0.1245149025846594</v>
       </c>
       <c r="C92">
-        <v>1.846245781134394</v>
+        <v>1.841067752210668</v>
       </c>
       <c r="D92">
-        <v>4.372245781134394</v>
+        <v>4.396667752210668</v>
       </c>
       <c r="E92">
-        <v>1.614</v>
+        <v>1.6436</v>
       </c>
       <c r="F92">
-        <v>2.664</v>
+        <v>2.6936</v>
       </c>
       <c r="G92">
         <v>0.138</v>
@@ -8825,28 +8825,28 @@
         <v>1.168</v>
       </c>
       <c r="M92">
-        <v>0.142524</v>
+        <v>0.1441076</v>
       </c>
       <c r="N92">
-        <v>1.025476</v>
+        <v>1.0238924</v>
       </c>
       <c r="O92">
-        <v>0.3076427999999999</v>
+        <v>0.3071677199999999</v>
       </c>
       <c r="P92">
-        <v>0.7178331999999998</v>
+        <v>0.7167246799999999</v>
       </c>
       <c r="Q92">
-        <v>0.7098331999999998</v>
+        <v>0.7087246799999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9124957893645309</v>
+        <v>1.004837806496216</v>
       </c>
       <c r="T92">
-        <v>6.042986603871219</v>
+        <v>6.686836013720512</v>
       </c>
       <c r="U92">
         <v>0.0535</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>8.195110998849316</v>
+        <v>8.105054834026795</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1245149025846594</v>
+        <v>0.1240752262328658</v>
       </c>
       <c r="C93">
-        <v>1.841067752210668</v>
+        <v>1.836164082459394</v>
       </c>
       <c r="D93">
-        <v>4.396667752210668</v>
+        <v>4.421364082459394</v>
       </c>
       <c r="E93">
-        <v>1.6436</v>
+        <v>1.6732</v>
       </c>
       <c r="F93">
-        <v>2.6936</v>
+        <v>2.7232</v>
       </c>
       <c r="G93">
         <v>0.138</v>
@@ -8907,28 +8907,28 @@
         <v>1.168</v>
       </c>
       <c r="M93">
-        <v>0.1441076</v>
+        <v>0.1456912</v>
       </c>
       <c r="N93">
-        <v>1.0238924</v>
+        <v>1.0223088</v>
       </c>
       <c r="O93">
-        <v>0.3071677199999999</v>
+        <v>0.3066926399999999</v>
       </c>
       <c r="P93">
-        <v>0.7167246799999999</v>
+        <v>0.7156161599999999</v>
       </c>
       <c r="Q93">
-        <v>0.7087246799999999</v>
+        <v>0.7076161599999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.004837806496216</v>
+        <v>1.120265327910823</v>
       </c>
       <c r="T93">
-        <v>6.686836013720512</v>
+        <v>7.491647776032131</v>
       </c>
       <c r="U93">
         <v>0.0535</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>8.105054834026795</v>
+        <v>8.016956411917807</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1240752262328658</v>
+        <v>0.1236355498810722</v>
       </c>
       <c r="C94">
-        <v>1.836164082459394</v>
+        <v>1.831539421269198</v>
       </c>
       <c r="D94">
-        <v>4.421364082459394</v>
+        <v>4.446339421269198</v>
       </c>
       <c r="E94">
-        <v>1.6732</v>
+        <v>1.7028</v>
       </c>
       <c r="F94">
-        <v>2.7232</v>
+        <v>2.7528</v>
       </c>
       <c r="G94">
         <v>0.138</v>
@@ -8989,28 +8989,28 @@
         <v>1.168</v>
       </c>
       <c r="M94">
-        <v>0.1456912</v>
+        <v>0.1472748</v>
       </c>
       <c r="N94">
-        <v>1.0223088</v>
+        <v>1.0207252</v>
       </c>
       <c r="O94">
-        <v>0.3066926399999999</v>
+        <v>0.30621756</v>
       </c>
       <c r="P94">
-        <v>0.7156161599999999</v>
+        <v>0.71450764</v>
       </c>
       <c r="Q94">
-        <v>0.7076161599999999</v>
+        <v>0.70650764</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.120265327910823</v>
+        <v>1.268672141158175</v>
       </c>
       <c r="T94">
-        <v>7.491647776032131</v>
+        <v>8.526405756147067</v>
       </c>
       <c r="U94">
         <v>0.0535</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>8.016956411917807</v>
+        <v>7.930752579531596</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1236355498810722</v>
+        <v>0.1231958735292785</v>
       </c>
       <c r="C95">
-        <v>1.831539421269198</v>
+        <v>1.827198523679102</v>
       </c>
       <c r="D95">
-        <v>4.446339421269198</v>
+        <v>4.471598523679102</v>
       </c>
       <c r="E95">
-        <v>1.7028</v>
+        <v>1.7324</v>
       </c>
       <c r="F95">
-        <v>2.7528</v>
+        <v>2.7824</v>
       </c>
       <c r="G95">
         <v>0.138</v>
@@ -9071,28 +9071,28 @@
         <v>1.168</v>
       </c>
       <c r="M95">
-        <v>0.1472748</v>
+        <v>0.1488584</v>
       </c>
       <c r="N95">
-        <v>1.0207252</v>
+        <v>1.0191416</v>
       </c>
       <c r="O95">
-        <v>0.30621756</v>
+        <v>0.30574248</v>
       </c>
       <c r="P95">
-        <v>0.71450764</v>
+        <v>0.7133991200000001</v>
       </c>
       <c r="Q95">
-        <v>0.70650764</v>
+        <v>0.70539912</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.268672141158175</v>
+        <v>1.466547892154643</v>
       </c>
       <c r="T95">
-        <v>8.526405756147067</v>
+        <v>9.906083062966983</v>
       </c>
       <c r="U95">
         <v>0.0535</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>7.930752579531596</v>
+        <v>7.846382871238707</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1231958735292785</v>
+        <v>0.1227561971774849</v>
       </c>
       <c r="C96">
-        <v>1.827198523679102</v>
+        <v>1.823146253396602</v>
       </c>
       <c r="D96">
-        <v>4.471598523679102</v>
+        <v>4.497146253396602</v>
       </c>
       <c r="E96">
-        <v>1.7324</v>
+        <v>1.762</v>
       </c>
       <c r="F96">
-        <v>2.7824</v>
+        <v>2.812</v>
       </c>
       <c r="G96">
         <v>0.138</v>
@@ -9153,28 +9153,28 @@
         <v>1.168</v>
       </c>
       <c r="M96">
-        <v>0.1488584</v>
+        <v>0.150442</v>
       </c>
       <c r="N96">
-        <v>1.0191416</v>
+        <v>1.017558</v>
       </c>
       <c r="O96">
-        <v>0.30574248</v>
+        <v>0.3052674</v>
       </c>
       <c r="P96">
-        <v>0.7133991200000001</v>
+        <v>0.7122906</v>
       </c>
       <c r="Q96">
-        <v>0.70539912</v>
+        <v>0.7042906</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.466547892154643</v>
+        <v>1.7435739435497</v>
       </c>
       <c r="T96">
-        <v>9.906083062966983</v>
+        <v>11.83763129251487</v>
       </c>
       <c r="U96">
         <v>0.0535</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>7.846382871238707</v>
+        <v>7.76378936733093</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1227561971774849</v>
+        <v>0.1223165208256912</v>
       </c>
       <c r="C97">
-        <v>1.823146253396602</v>
+        <v>1.819387585919813</v>
       </c>
       <c r="D97">
-        <v>4.497146253396602</v>
+        <v>4.522987585919814</v>
       </c>
       <c r="E97">
-        <v>1.762</v>
+        <v>1.7916</v>
       </c>
       <c r="F97">
-        <v>2.812</v>
+        <v>2.8416</v>
       </c>
       <c r="G97">
         <v>0.138</v>
@@ -9235,28 +9235,28 @@
         <v>1.168</v>
       </c>
       <c r="M97">
-        <v>0.150442</v>
+        <v>0.1520256</v>
       </c>
       <c r="N97">
-        <v>1.017558</v>
+        <v>1.0159744</v>
       </c>
       <c r="O97">
-        <v>0.3052674</v>
+        <v>0.3047923199999999</v>
       </c>
       <c r="P97">
-        <v>0.7122906</v>
+        <v>0.7111820799999999</v>
       </c>
       <c r="Q97">
-        <v>0.7042906</v>
+        <v>0.7031820799999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.7435739435497</v>
+        <v>2.159113020642285</v>
       </c>
       <c r="T97">
-        <v>11.83763129251487</v>
+        <v>14.7349536368367</v>
       </c>
       <c r="U97">
         <v>0.0535</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>7.76378936733093</v>
+        <v>7.682916561421234</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1223165208256912</v>
+        <v>0.1224200444738976</v>
       </c>
       <c r="C98">
-        <v>1.819387585919814</v>
+        <v>1.783676441259148</v>
       </c>
       <c r="D98">
-        <v>4.522987585919814</v>
+        <v>4.516876441259148</v>
       </c>
       <c r="E98">
-        <v>1.7916</v>
+        <v>1.8212</v>
       </c>
       <c r="F98">
-        <v>2.8416</v>
+        <v>2.8712</v>
       </c>
       <c r="G98">
         <v>0.138</v>
@@ -9317,45 +9317,45 @@
         <v>1.168</v>
       </c>
       <c r="M98">
-        <v>0.1520256</v>
+        <v>0.15590616</v>
       </c>
       <c r="N98">
-        <v>1.0159744</v>
+        <v>1.01209384</v>
       </c>
       <c r="O98">
-        <v>0.3047923199999999</v>
+        <v>0.303628152</v>
       </c>
       <c r="P98">
-        <v>0.7111820799999999</v>
+        <v>0.708465688</v>
       </c>
       <c r="Q98">
-        <v>0.7031820799999999</v>
+        <v>0.700465688</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.159113020642279</v>
+        <v>2.851678149129917</v>
       </c>
       <c r="T98">
-        <v>14.73495363683666</v>
+        <v>19.56382421070635</v>
       </c>
       <c r="U98">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V98">
         <v>0.3</v>
       </c>
       <c r="W98">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y98">
-        <v>7.682916561421234</v>
+        <v>7.491686024464973</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1224200444738976</v>
+        <v>0.1219859681221039</v>
       </c>
       <c r="C99">
-        <v>1.783676441259148</v>
+        <v>1.779811747844505</v>
       </c>
       <c r="D99">
-        <v>4.516876441259148</v>
+        <v>4.542611747844504</v>
       </c>
       <c r="E99">
-        <v>1.8212</v>
+        <v>1.8508</v>
       </c>
       <c r="F99">
-        <v>2.8712</v>
+        <v>2.9008</v>
       </c>
       <c r="G99">
         <v>0.138</v>
@@ -9399,28 +9399,28 @@
         <v>1.168</v>
       </c>
       <c r="M99">
-        <v>0.15590616</v>
+        <v>0.15751344</v>
       </c>
       <c r="N99">
-        <v>1.01209384</v>
+        <v>1.01048656</v>
       </c>
       <c r="O99">
-        <v>0.303628152</v>
+        <v>0.303145968</v>
       </c>
       <c r="P99">
-        <v>0.708465688</v>
+        <v>0.707340592</v>
       </c>
       <c r="Q99">
-        <v>0.700465688</v>
+        <v>0.699340592</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.851678149129917</v>
+        <v>4.236808406105194</v>
       </c>
       <c r="T99">
-        <v>19.56382421070635</v>
+        <v>29.22156535844573</v>
       </c>
       <c r="U99">
         <v>0.0543</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>7.491686024464973</v>
+        <v>7.415240248705126</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1219859681221039</v>
+        <v>0.1215518917703103</v>
       </c>
       <c r="C100">
-        <v>1.779811747844505</v>
+        <v>1.776241993281781</v>
       </c>
       <c r="D100">
-        <v>4.542611747844504</v>
+        <v>4.568641993281782</v>
       </c>
       <c r="E100">
-        <v>1.8508</v>
+        <v>1.8804</v>
       </c>
       <c r="F100">
-        <v>2.9008</v>
+        <v>2.9304</v>
       </c>
       <c r="G100">
         <v>0.138</v>
@@ -9481,28 +9481,28 @@
         <v>1.168</v>
       </c>
       <c r="M100">
-        <v>0.15751344</v>
+        <v>0.15912072</v>
       </c>
       <c r="N100">
-        <v>1.01048656</v>
+        <v>1.00887928</v>
       </c>
       <c r="O100">
-        <v>0.303145968</v>
+        <v>0.302663784</v>
       </c>
       <c r="P100">
-        <v>0.707340592</v>
+        <v>0.706215496</v>
       </c>
       <c r="Q100">
-        <v>0.699340592</v>
+        <v>0.698215496</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.236808406105194</v>
+        <v>8.392199177031024</v>
       </c>
       <c r="T100">
-        <v>29.22156535844573</v>
+        <v>58.19478880166388</v>
       </c>
       <c r="U100">
         <v>0.0543</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>7.415240248705126</v>
+        <v>7.340338832051538</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1215518917703103</v>
-      </c>
-      <c r="C101">
-        <v>1.776241993281781</v>
-      </c>
-      <c r="D101">
-        <v>4.568641993281782</v>
-      </c>
-      <c r="E101">
-        <v>1.8804</v>
-      </c>
-      <c r="F101">
-        <v>2.9304</v>
-      </c>
-      <c r="G101">
-        <v>0.138</v>
-      </c>
-      <c r="H101">
-        <v>1.91</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.16</v>
-      </c>
-      <c r="K101">
-        <v>-0.008</v>
-      </c>
-      <c r="L101">
-        <v>1.168</v>
-      </c>
-      <c r="M101">
-        <v>0.15912072</v>
-      </c>
-      <c r="N101">
-        <v>1.00887928</v>
-      </c>
-      <c r="O101">
-        <v>0.302663784</v>
-      </c>
-      <c r="P101">
-        <v>0.706215496</v>
-      </c>
-      <c r="Q101">
-        <v>0.698215496</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.392199177031024</v>
-      </c>
-      <c r="T101">
-        <v>58.19478880166388</v>
-      </c>
-      <c r="U101">
-        <v>0.0543</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.03801</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A2/A</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>7.340338832051538</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
